--- a/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
@@ -766,10 +766,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -821,22 +821,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -983,22 +983,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>03/17/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>Oscar Health</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Oscar Health</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>03/17/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -1096,22 +1096,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>03/17/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>Oscar Health</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Oscar Health</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>03/17/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -1209,22 +1209,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>03/31/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -1326,22 +1326,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>Mutual of Omaha Insurance Company</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Mutual of Omaha Insurance Company</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>03/02/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -1445,22 +1445,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>Mutual of Omaha Insurance Company</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Mutual of Omaha Insurance Company</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>03/02/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -1564,22 +1564,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -1683,22 +1683,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>03/11/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>03/11/2026</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -1921,22 +1921,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>03/11/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>03/11/2026</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -2036,22 +2036,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>03/12/2026</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -2145,22 +2145,22 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>03/12/2026</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -2258,22 +2258,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>03/13/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>Bankers Life Colonial Penn Life</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>Bankers Life Colonial Penn Life</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>03/13/2026</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -2377,22 +2377,22 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>03/13/2026</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
           <t>Bankers Life Colonial Penn Life</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Bankers Life Colonial Penn Life</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>03/13/2026</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -2496,22 +2496,22 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
+          <t>03/13/2026</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
           <t>ChampVA - HAC</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>ChampVA - HAC</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>03/13/2026</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -2615,22 +2615,22 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
+          <t>03/13/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
           <t>ChampVA - HAC</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>ChampVA - HAC</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>03/13/2026</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -2734,22 +2734,22 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
+          <t>03/27/2026</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
           <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>03/27/2026</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -2853,22 +2853,22 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
+          <t>03/27/2026</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
           <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>03/27/2026</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -2968,22 +2968,22 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
+          <t>03/27/2026</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>03/27/2026</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -3077,22 +3077,22 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
+          <t>03/27/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>03/27/2026</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>03/30/2026</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Banner Medicare Advantage Prime HMO (BMAH)</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>03/30/2026</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -3299,22 +3299,22 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
+          <t>03/30/2026</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>Banner Medicare Advantage Prime HMO (BMAH)</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>03/30/2026</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -3412,22 +3412,22 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -3529,22 +3529,22 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -3646,22 +3646,22 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -3759,22 +3759,22 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -3876,22 +3876,22 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -3995,22 +3995,22 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -4110,22 +4110,22 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -4223,22 +4223,22 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
@@ -4336,22 +4336,22 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
+          <t>03/11/2026</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>03/11/2026</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
@@ -4449,22 +4449,22 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
+          <t>03/11/2026</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>03/11/2026</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -4562,22 +4562,22 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
+          <t>03/13/2026</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>03/13/2026</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -4679,22 +4679,22 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
+          <t>03/13/2026</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>03/13/2026</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -4792,22 +4792,22 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
+          <t>03/16/2026</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>03/16/2026</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -4913,22 +4913,22 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
+          <t>03/16/2026</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>03/16/2026</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
@@ -5034,22 +5034,22 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
+          <t>03/18/2026</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
@@ -5147,22 +5147,22 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
+          <t>03/18/2026</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
@@ -5260,22 +5260,22 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
+          <t>03/18/2026</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
@@ -5377,22 +5377,22 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
+          <t>03/18/2026</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G40" s="5" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
@@ -5498,22 +5498,22 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
+          <t>03/20/2026</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>03/20/2026</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
@@ -5615,22 +5615,22 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
+          <t>03/20/2026</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>03/20/2026</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
@@ -5728,22 +5728,22 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
+          <t>03/20/2026</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="H43" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>03/20/2026</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
@@ -5845,22 +5845,22 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
+          <t>03/20/2026</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="H44" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>03/20/2026</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
@@ -5962,22 +5962,22 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
+          <t>03/23/2026</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>03/23/2026</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
@@ -6083,22 +6083,22 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
+          <t>03/25/2026</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
           <t>ChampVA - HAC</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="G46" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>ChampVA - HAC</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>03/25/2026</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
@@ -6202,22 +6202,22 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
+          <t>03/27/2026</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>03/27/2026</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
@@ -6315,22 +6315,22 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
+          <t>03/27/2026</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="G48" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>03/27/2026</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
@@ -6428,22 +6428,22 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
+          <t>03/27/2026</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>03/27/2026</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
@@ -6541,22 +6541,22 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
+          <t>03/27/2026</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="G50" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>03/27/2026</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
@@ -6658,22 +6658,22 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
+          <t>03/19/2026</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
           <t>Banner Aetna</t>
         </is>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>Banner Aetna</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="H51" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>03/19/2026</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
@@ -6771,22 +6771,22 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
+          <t>03/19/2026</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
           <t>Banner Aetna</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="G52" s="5" t="inlineStr">
         <is>
           <t>Banner Aetna</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="H52" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>03/19/2026</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
@@ -6884,22 +6884,22 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
+          <t>03/18/2026</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
@@ -6995,22 +6995,22 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
+          <t>03/18/2026</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>Alignment Health Care</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
@@ -7106,22 +7106,22 @@
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
+          <t>03/20/2026</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
           <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>03/20/2026</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
@@ -7209,22 +7209,22 @@
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
+          <t>03/20/2026</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
           <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="H56" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>03/20/2026</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
@@ -7320,22 +7320,22 @@
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
+          <t>03/23/2026</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
           <t>Banner University Family Care - Arizona Long Term Care System</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>Banner University Care Dual Advantage Plan</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="H57" s="5" t="inlineStr">
         <is>
           <t>Banner University Family Care - Arizona Long Term Care System</t>
-        </is>
-      </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>03/23/2026</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
@@ -7437,22 +7437,22 @@
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
+          <t>03/23/2026</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
           <t>Banner University Family Care - Arizona Long Term Care System</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr">
         <is>
           <t>Banner University Care Dual Advantage Plan</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="H58" s="5" t="inlineStr">
         <is>
           <t>Banner University Family Care - Arizona Long Term Care System</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>03/23/2026</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
@@ -7550,22 +7550,22 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
+          <t>03/27/2026</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
           <t>Imperial Insurance Companies Inc Exchange AZ (IEXAZ) (WAYSTAR ONLY)</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="G59" s="5" t="inlineStr">
         <is>
           <t>Imperial Insurance Companies Inc Exchange AZ (IEXAZ) (WAYSTAR ONLY)</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr">
+      <c r="H59" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>03/27/2026</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
@@ -7657,22 +7657,22 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
+          <t>03/27/2026</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
           <t>Imperial Insurance Companies Inc Exchange AZ (IEXAZ) (WAYSTAR ONLY)</t>
         </is>
       </c>
-      <c r="F60" s="5" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr">
         <is>
           <t>Imperial Insurance Companies Inc Exchange AZ (IEXAZ) (WAYSTAR ONLY)</t>
         </is>
       </c>
-      <c r="G60" s="5" t="inlineStr">
+      <c r="H60" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>03/27/2026</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
@@ -7793,10 +7793,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -7848,22 +7848,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -8010,22 +8010,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>MediCo Insurance Company</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -8127,22 +8127,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>03/16/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Humana</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>03/16/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -8252,22 +8252,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>03/16/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>BANKERS FIDELITY</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>03/16/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -8373,22 +8373,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>03/23/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Humana</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>03/23/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -8498,22 +8498,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>03/23/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>Medicare Railroad (RR Medicare MetraHealth) 00882</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Medicare Railroad (RR Medicare MetraHealth) 00882</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>03/23/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -8623,22 +8623,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>03/30/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>03/30/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -8744,22 +8744,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>DME Region D</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Aetna Senior Supplemental (AESSI) - Secondary Only 62118</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>03/31/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -8869,22 +8869,22 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>03/11/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>03/11/2026</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -8986,22 +8986,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>03/16/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>03/16/2026</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -9111,22 +9111,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>03/26/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare / All Savers Insurance</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare / All Savers Insurance</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>03/26/2026</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -9267,10 +9267,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -9322,22 +9322,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -9484,22 +9484,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>03/02/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -9617,22 +9617,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>03/02/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -9746,22 +9746,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>03/02/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -9879,22 +9879,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>AMETrust</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>AMETrust</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -10006,22 +10006,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Arizona Complete Health (Centene)</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -10125,22 +10125,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Arizona Complete Health (Centene)</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -10240,22 +10240,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Arizona Complete Health (Centene)</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -10355,22 +10355,22 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Arizona Complete Health (Centene)</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -10470,22 +10470,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Arizona Complete Health (Centene)</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -10585,22 +10585,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Arizona Complete Health (Centene)</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -10704,22 +10704,22 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>UMR Wausau / UHIS</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>Arizona Complete Health (Centene)</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -10844,10 +10844,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -10899,22 +10899,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -11061,22 +11061,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>03/02/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>03/02/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -11178,22 +11178,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -11303,22 +11303,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -11432,22 +11432,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>03/13/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>03/13/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -11551,22 +11551,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>03/18/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -11668,22 +11668,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>03/23/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>03/23/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -11789,22 +11789,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>03/23/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>03/23/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -11910,22 +11910,22 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>03/23/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>03/23/2026</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -12039,22 +12039,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>03/25/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>ChampVA - HAC</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>ChampVA - HAC</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>03/25/2026</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -12158,22 +12158,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>03/27/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Mercy Care Plan (AHCCCS) - Complete Care &amp; Long Term Care (LTC)</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>03/27/2026</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -12277,22 +12277,22 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>HealthSpring Medicare Advantage</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -12402,22 +12402,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -12519,22 +12519,22 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -12636,22 +12636,22 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -12753,22 +12753,22 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -12874,22 +12874,22 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>03/12/2026</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -12995,22 +12995,22 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>03/12/2026</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -13120,22 +13120,22 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>03/12/2026</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -13241,22 +13241,22 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>03/12/2026</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -13362,22 +13362,22 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>03/12/2026</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -13483,22 +13483,22 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>03/12/2026</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -13600,22 +13600,22 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
+          <t>03/12/2026</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>03/12/2026</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -13717,22 +13717,22 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
+          <t>03/16/2026</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>03/16/2026</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
@@ -13850,22 +13850,22 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
+          <t>03/16/2026</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Humana</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>03/16/2026</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
@@ -13983,22 +13983,22 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
+          <t>03/20/2026</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
           <t>Aetna Legacy</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Aetna Legacy</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>03/20/2026</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -14129,10 +14129,10 @@
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
@@ -14184,22 +14184,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Responsible Payer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Primary Payer Name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Secondary Payer Name</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Date of Service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
+          <t>03/17/2026</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
           <t>Mercy Care RBHA</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Mercy Care RBHA</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>03/17/2026</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -14463,22 +14463,22 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
+          <t>03/17/2026</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
           <t>Mercy Care RBHA</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Mercy Care RBHA</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>03/17/2026</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -14580,22 +14580,22 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
+          <t>03/10/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>AARP United Healthcare</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>03/10/2026</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -14701,22 +14701,22 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>03/31/2026</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
@@ -14818,22 +14818,22 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>03/31/2026</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -14939,22 +14939,22 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
+          <t>03/03/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
           <t>Banner Health Physician Hospital Organization Plan Administration</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Banner Health Physician Hospital Organization Plan Administration</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>03/03/2026</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -15064,22 +15064,22 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
+          <t>03/03/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
           <t>CIGNA HealthSprings</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>CIGNA HealthSprings</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>03/03/2026</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -15189,22 +15189,22 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
+          <t>03/03/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
           <t>CIGNA HealthSprings</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>CIGNA HealthSprings</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>03/03/2026</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -15314,22 +15314,22 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
+          <t>03/17/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>United Healthcare</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>03/17/2026</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -15435,22 +15435,22 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
+          <t>03/18/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
@@ -15564,22 +15564,22 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>03/18/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -15693,22 +15693,22 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>03/18/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Humana Gold Plus HMO</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -15826,22 +15826,22 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
+          <t>03/18/2026</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
           <t>Tricare West</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>CIGNA HealthSprings</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Tricare West</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>03/18/2026</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -15941,22 +15941,22 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
+          <t>03/24/2026</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
           <t>CIGNA HealthSprings</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>CIGNA HealthSprings</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>03/24/2026</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -16058,22 +16058,22 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
+          <t>03/24/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>03/24/2026</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -16179,22 +16179,22 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
           <t>Aetna Medicare PPO</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Aetna Medicare PPO</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -16300,22 +16300,22 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
           <t>Aetna Medicare PPO</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Aetna Medicare PPO</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
@@ -16421,22 +16421,22 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
+          <t>03/11/2026</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
           <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Banner Health &amp; Aetna Health Insurance Company</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>03/11/2026</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -16538,22 +16538,22 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
           <t>Aetna Medicare PPO</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Aetna Medicare PPO</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>03/31/2026</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
@@ -16659,22 +16659,22 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
+          <t>03/17/2026</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
           <t>AARP MedicareComplete (SecureHorizons &amp; Oxford Network)</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>AARP MedicareComplete (SecureHorizons &amp; Oxford Network)</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>03/17/2026</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
@@ -16770,22 +16770,22 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
+          <t>03/17/2026</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
           <t>AARP MedicareComplete (SecureHorizons &amp; Oxford Network)</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>AARP MedicareComplete (SecureHorizons &amp; Oxford Network)</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>03/17/2026</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -16881,22 +16881,22 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
+          <t>03/17/2026</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
           <t>AARP MedicareComplete (SecureHorizons &amp; Oxford Network)</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>AARP MedicareComplete (SecureHorizons &amp; Oxford Network)</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>No Payer</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>03/17/2026</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">

--- a/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
@@ -1271,26 +1271,26 @@
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="5" t="n">
-        <v>554404221</v>
+        <v>553329086</v>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>HF525117988</t>
+          <t>HF524312806</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>03/31/2026</t>
+          <t>03/20/2026</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>TRIWEST VA CCN CLAIMS</t>
+          <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>TRIWEST VA CCN CLAIMS</t>
+          <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K4" s="4" t="n"/>
@@ -1309,7 +1309,7 @@
         <v/>
       </c>
       <c r="M4" s="7" t="n">
-        <v>46292</v>
+        <v>46281</v>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>VETERANS ADMIN (VA CCN)</t>
+          <t>MEDICA</t>
         </is>
       </c>
       <c r="P4" s="6" t="n"/>
@@ -1328,7 +1328,7 @@
         <v>1</v>
       </c>
       <c r="T4" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="U4" s="8" t="n">
         <v>0</v>
@@ -1336,20 +1336,16 @@
       <c r="V4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="W4" s="6" t="inlineStr">
-        <is>
-          <t>04/16/2026</t>
-        </is>
-      </c>
+      <c r="W4" s="6" t="n"/>
       <c r="X4" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="Y4" s="5" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="Z4" s="6" t="inlineStr">
         <is>
-          <t>F4320</t>
+          <t>F411</t>
         </is>
       </c>
       <c r="AA4" s="6" t="n"/>
@@ -1358,12 +1354,12 @@
       <c r="AD4" s="5" t="n"/>
       <c r="AE4" s="6" t="inlineStr">
         <is>
-          <t>LEATHEM, JARRETT</t>
+          <t>MEARS, CHAD</t>
         </is>
       </c>
       <c r="AF4" s="6" t="inlineStr">
         <is>
-          <t>ASAP Peoria</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG4" s="6" t="inlineStr">
@@ -1376,50 +1372,50 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI4" s="9" t="n"/>
+      <c r="AI4" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 180 days from DOS; 180 days from the Medicare payment date for Select Solution and Prime Solution.</t>
+        </is>
+      </c>
       <c r="AJ4" s="5" t="n">
-        <v>105</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Finalized</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="n"/>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="5" t="n">
-        <v>551389428</v>
+        <v>553329086</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>HF549983763</t>
+          <t>HF524312806</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>03/20/2026</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>Mutual of Omaha Insurance Company</t>
+          <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>Medicare Part B Arizona *</t>
+          <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>Mutual of Omaha Insurance Company</t>
+          <t>No Payer</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="K5" s="4" t="n"/>
@@ -1428,16 +1424,16 @@
         <v/>
       </c>
       <c r="M5" s="7" t="n">
-        <v>46448</v>
+        <v>46281</v>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>365 days</t>
+          <t>180 days</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>MEDICARE</t>
+          <t>MEDICA</t>
         </is>
       </c>
       <c r="P5" s="6" t="n"/>
@@ -1447,44 +1443,42 @@
         <v>1</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>329.26</v>
+        <v>0</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>54.97</v>
+        <v>0</v>
       </c>
       <c r="W5" s="6" t="inlineStr">
         <is>
-          <t>04/29/2026</t>
+          <t>04/17/2026</t>
         </is>
       </c>
       <c r="X5" s="8" t="n">
-        <v>12.04</v>
+        <v>976.64</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="Z5" s="6" t="inlineStr">
         <is>
-          <t>F4320</t>
+          <t>F411</t>
         </is>
       </c>
       <c r="AA5" s="6" t="n"/>
       <c r="AB5" s="6" t="n"/>
       <c r="AC5" s="6" t="n"/>
-      <c r="AD5" s="5" t="n">
-        <v>559119307</v>
-      </c>
+      <c r="AD5" s="5" t="n"/>
       <c r="AE5" s="6" t="inlineStr">
         <is>
-          <t>TURLEY, TODD</t>
+          <t>MEARS, CHAD</t>
         </is>
       </c>
       <c r="AF5" s="6" t="inlineStr">
         <is>
-          <t>ASAP Peoria</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG5" s="6" t="inlineStr">
@@ -1497,9 +1491,13 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI5" s="9" t="n"/>
+      <c r="AI5" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 180 days from DOS; 180 days from the Medicare payment date for Select Solution and Prime Solution.</t>
+        </is>
+      </c>
       <c r="AJ5" s="5" t="n">
-        <v>279</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6">
@@ -1540,7 +1538,7 @@
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K6" s="4" t="n"/>
@@ -1568,13 +1566,13 @@
         <v>1</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>855.4299999999999</v>
+        <v>329.26</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>143.2</v>
+        <v>54.97</v>
       </c>
       <c r="W6" s="6" t="inlineStr">
         <is>
@@ -1582,7 +1580,7 @@
         </is>
       </c>
       <c r="X6" s="8" t="n">
-        <v>31.35</v>
+        <v>12.04</v>
       </c>
       <c r="Y6" s="5" t="n">
         <v>159</v>
@@ -1620,7 +1618,7 @@
       </c>
       <c r="AI6" s="9" t="n"/>
       <c r="AJ6" s="5" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7">
@@ -1632,21 +1630,21 @@
       <c r="B7" s="3" t="n"/>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="5" t="n">
-        <v>551962197</v>
+        <v>551389428</v>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>HF470696196</t>
+          <t>HF549983763</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>Mutual of Omaha Insurance Company</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -1656,12 +1654,12 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>Mutual of Omaha Insurance Company</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="K7" s="4" t="n"/>
@@ -1670,7 +1668,7 @@
         <v/>
       </c>
       <c r="M7" s="7" t="n">
-        <v>46452</v>
+        <v>46448</v>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
@@ -1689,44 +1687,44 @@
         <v>1</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>976.64</v>
+        <v>1029.98</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>836.85</v>
+        <v>855.4299999999999</v>
       </c>
       <c r="V7" s="8" t="n">
-        <v>111.38</v>
+        <v>143.2</v>
       </c>
       <c r="W7" s="6" t="inlineStr">
         <is>
-          <t>04/22/2026</t>
+          <t>04/29/2026</t>
         </is>
       </c>
       <c r="X7" s="8" t="n">
-        <v>28.41</v>
+        <v>31.35</v>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="Z7" s="6" t="inlineStr">
         <is>
-          <t>F4321</t>
+          <t>F4320</t>
         </is>
       </c>
       <c r="AA7" s="6" t="n"/>
       <c r="AB7" s="6" t="n"/>
       <c r="AC7" s="6" t="n"/>
       <c r="AD7" s="5" t="n">
-        <v>559120111</v>
+        <v>559119307</v>
       </c>
       <c r="AE7" s="6" t="inlineStr">
         <is>
-          <t>SARKAR, AWNIK</t>
+          <t>TURLEY, TODD</t>
         </is>
       </c>
       <c r="AF7" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY</t>
+          <t>ASAP Peoria</t>
         </is>
       </c>
       <c r="AG7" s="6" t="inlineStr">
@@ -1741,7 +1739,7 @@
       </c>
       <c r="AI7" s="9" t="n"/>
       <c r="AJ7" s="5" t="n">
-        <v>7</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8">
@@ -1782,7 +1780,7 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="K8" s="4" t="n"/>
@@ -1807,16 +1805,16 @@
       <c r="Q8" s="6" t="n"/>
       <c r="R8" s="6" t="n"/>
       <c r="S8" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>792.54</v>
+        <v>976.64</v>
       </c>
       <c r="U8" s="8" t="n">
-        <v>674.11</v>
+        <v>836.85</v>
       </c>
       <c r="V8" s="8" t="n">
-        <v>94.36</v>
+        <v>111.38</v>
       </c>
       <c r="W8" s="6" t="inlineStr">
         <is>
@@ -1824,7 +1822,7 @@
         </is>
       </c>
       <c r="X8" s="8" t="n">
-        <v>24.07</v>
+        <v>28.41</v>
       </c>
       <c r="Y8" s="5" t="n">
         <v>155</v>
@@ -1862,7 +1860,7 @@
       </c>
       <c r="AI8" s="9" t="n"/>
       <c r="AJ8" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -1874,16 +1872,16 @@
       <c r="B9" s="3" t="n"/>
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="5" t="n">
-        <v>552404210</v>
+        <v>551962197</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>HF364689537</t>
+          <t>HF470696196</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>03/11/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -1903,7 +1901,7 @@
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K9" s="4" t="n"/>
@@ -1912,7 +1910,7 @@
         <v/>
       </c>
       <c r="M9" s="7" t="n">
-        <v>46457</v>
+        <v>46452</v>
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
@@ -1928,42 +1926,42 @@
       <c r="Q9" s="6" t="n"/>
       <c r="R9" s="6" t="n"/>
       <c r="S9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T9" s="8" t="n">
-        <v>976.64</v>
+        <v>792.54</v>
       </c>
       <c r="U9" s="8" t="n">
-        <v>818.47</v>
+        <v>674.11</v>
       </c>
       <c r="V9" s="8" t="n">
-        <v>129.76</v>
+        <v>94.36</v>
       </c>
       <c r="W9" s="6" t="inlineStr">
         <is>
-          <t>04/29/2026</t>
+          <t>04/22/2026</t>
         </is>
       </c>
       <c r="X9" s="8" t="n">
-        <v>28.41</v>
+        <v>24.07</v>
       </c>
       <c r="Y9" s="5" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="Z9" s="6" t="inlineStr">
         <is>
-          <t>F330</t>
+          <t>F4321</t>
         </is>
       </c>
       <c r="AA9" s="6" t="n"/>
       <c r="AB9" s="6" t="n"/>
       <c r="AC9" s="6" t="n"/>
       <c r="AD9" s="5" t="n">
-        <v>559120113</v>
+        <v>559120111</v>
       </c>
       <c r="AE9" s="6" t="inlineStr">
         <is>
-          <t>TURLEY, TODD</t>
+          <t>SARKAR, AWNIK</t>
         </is>
       </c>
       <c r="AF9" s="6" t="inlineStr">
@@ -1983,7 +1981,7 @@
       </c>
       <c r="AI9" s="9" t="n"/>
       <c r="AJ9" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -2024,7 +2022,7 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="K10" s="4" t="n"/>
@@ -2052,13 +2050,13 @@
         <v>1</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>329.26</v>
+        <v>818.47</v>
       </c>
       <c r="V10" s="8" t="n">
-        <v>54.97</v>
+        <v>129.76</v>
       </c>
       <c r="W10" s="6" t="inlineStr">
         <is>
@@ -2066,7 +2064,7 @@
         </is>
       </c>
       <c r="X10" s="8" t="n">
-        <v>12.04</v>
+        <v>28.41</v>
       </c>
       <c r="Y10" s="5" t="n">
         <v>150</v>
@@ -2104,44 +2102,48 @@
       </c>
       <c r="AI10" s="9" t="n"/>
       <c r="AJ10" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Finalized</t>
+        </is>
+      </c>
       <c r="B11" s="3" t="n"/>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="5" t="n">
-        <v>552644739</v>
+        <v>552404210</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>HF550420682</t>
+          <t>HF364689537</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>03/12/2026</t>
+          <t>03/11/2026</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Medicare Part B Arizona *</t>
-        </is>
-      </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>AARP United Healthcare</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K11" s="4" t="n"/>
@@ -2150,7 +2152,7 @@
         <v/>
       </c>
       <c r="M11" s="7" t="n">
-        <v>46458</v>
+        <v>46457</v>
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
@@ -2169,33 +2171,39 @@
         <v>1</v>
       </c>
       <c r="T11" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="U11" s="8" t="n">
-        <v>0</v>
+        <v>329.26</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" s="6" t="n"/>
+        <v>54.97</v>
+      </c>
+      <c r="W11" s="6" t="inlineStr">
+        <is>
+          <t>04/29/2026</t>
+        </is>
+      </c>
       <c r="X11" s="8" t="n">
-        <v>1029.98</v>
+        <v>12.04</v>
       </c>
       <c r="Y11" s="5" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Z11" s="6" t="inlineStr">
         <is>
-          <t>F1190</t>
+          <t>F330</t>
         </is>
       </c>
       <c r="AA11" s="6" t="n"/>
       <c r="AB11" s="6" t="n"/>
       <c r="AC11" s="6" t="n"/>
-      <c r="AD11" s="5" t="n"/>
+      <c r="AD11" s="5" t="n">
+        <v>559120113</v>
+      </c>
       <c r="AE11" s="6" t="inlineStr">
         <is>
-          <t>KRAUSE, JEFFREY</t>
+          <t>TURLEY, TODD</t>
         </is>
       </c>
       <c r="AF11" s="6" t="inlineStr">
@@ -2215,7 +2223,7 @@
       </c>
       <c r="AI11" s="9" t="n"/>
       <c r="AJ11" s="5" t="n">
-        <v>467</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -2252,7 +2260,7 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="K12" s="4" t="n"/>
@@ -2280,7 +2288,7 @@
         <v>1</v>
       </c>
       <c r="T12" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="U12" s="8" t="n">
         <v>0</v>
@@ -2290,7 +2298,7 @@
       </c>
       <c r="W12" s="6" t="n"/>
       <c r="X12" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="Y12" s="5" t="n">
         <v>149</v>
@@ -2326,33 +2334,29 @@
       </c>
       <c r="AI12" s="9" t="n"/>
       <c r="AJ12" s="5" t="n">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Finalized</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="n"/>
       <c r="B13" s="3" t="n"/>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="5" t="n">
-        <v>552606577</v>
+        <v>552644739</v>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>HF544007270</t>
+          <t>HF550420682</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>03/13/2026</t>
+          <t>03/12/2026</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Bankers Life Colonial Penn Life</t>
+          <t>Medicare Part B Arizona *</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -2362,7 +2366,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>Bankers Life Colonial Penn Life</t>
+          <t>AARP United Healthcare</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
@@ -2376,7 +2380,7 @@
         <v/>
       </c>
       <c r="M13" s="7" t="n">
-        <v>46459</v>
+        <v>46458</v>
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
@@ -2398,41 +2402,35 @@
         <v>396.27</v>
       </c>
       <c r="U13" s="8" t="n">
-        <v>329.26</v>
+        <v>0</v>
       </c>
       <c r="V13" s="8" t="n">
-        <v>54.97</v>
-      </c>
-      <c r="W13" s="6" t="inlineStr">
-        <is>
-          <t>04/29/2026</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W13" s="6" t="n"/>
       <c r="X13" s="8" t="n">
-        <v>12.04</v>
+        <v>396.27</v>
       </c>
       <c r="Y13" s="5" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Z13" s="6" t="inlineStr">
         <is>
-          <t>F39</t>
+          <t>F1190</t>
         </is>
       </c>
       <c r="AA13" s="6" t="n"/>
       <c r="AB13" s="6" t="n"/>
       <c r="AC13" s="6" t="n"/>
-      <c r="AD13" s="5" t="n">
-        <v>559120100</v>
-      </c>
+      <c r="AD13" s="5" t="n"/>
       <c r="AE13" s="6" t="inlineStr">
         <is>
-          <t>LEATHEM, JARRETT</t>
+          <t>KRAUSE, JEFFREY</t>
         </is>
       </c>
       <c r="AF13" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - DEER VALLEY</t>
         </is>
       </c>
       <c r="AG13" s="6" t="inlineStr">
@@ -2447,7 +2445,7 @@
       </c>
       <c r="AI13" s="9" t="n"/>
       <c r="AJ13" s="5" t="n">
-        <v>178</v>
+        <v>468</v>
       </c>
     </row>
     <row r="14">
@@ -2488,7 +2486,7 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K14" s="4" t="n"/>
@@ -2516,13 +2514,13 @@
         <v>1</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>855.4299999999999</v>
+        <v>329.26</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>143.2</v>
+        <v>54.97</v>
       </c>
       <c r="W14" s="6" t="inlineStr">
         <is>
@@ -2530,7 +2528,7 @@
         </is>
       </c>
       <c r="X14" s="8" t="n">
-        <v>31.35</v>
+        <v>12.04</v>
       </c>
       <c r="Y14" s="5" t="n">
         <v>148</v>
@@ -2568,7 +2566,7 @@
       </c>
       <c r="AI14" s="9" t="n"/>
       <c r="AJ14" s="5" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15">
@@ -2580,11 +2578,11 @@
       <c r="B15" s="3" t="n"/>
       <c r="C15" s="4" t="n"/>
       <c r="D15" s="5" t="n">
-        <v>552857208</v>
+        <v>552606577</v>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>HF419012518</t>
+          <t>HF544007270</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -2594,7 +2592,7 @@
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>ChampVA - HAC</t>
+          <t>Bankers Life Colonial Penn Life</t>
         </is>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -2604,7 +2602,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>ChampVA - HAC</t>
+          <t>Bankers Life Colonial Penn Life</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
@@ -2640,14 +2638,14 @@
         <v>1029.98</v>
       </c>
       <c r="U15" s="8" t="n">
-        <v>883.59</v>
+        <v>855.4299999999999</v>
       </c>
       <c r="V15" s="8" t="n">
-        <v>115.04</v>
+        <v>143.2</v>
       </c>
       <c r="W15" s="6" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>04/29/2026</t>
         </is>
       </c>
       <c r="X15" s="8" t="n">
@@ -2658,23 +2656,23 @@
       </c>
       <c r="Z15" s="6" t="inlineStr">
         <is>
-          <t>F4320</t>
+          <t>F39</t>
         </is>
       </c>
       <c r="AA15" s="6" t="n"/>
       <c r="AB15" s="6" t="n"/>
       <c r="AC15" s="6" t="n"/>
       <c r="AD15" s="5" t="n">
-        <v>559120090</v>
+        <v>559120100</v>
       </c>
       <c r="AE15" s="6" t="inlineStr">
         <is>
-          <t>O'NEIL, ROY</t>
+          <t>LEATHEM, JARRETT</t>
         </is>
       </c>
       <c r="AF15" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG15" s="6" t="inlineStr">
@@ -2689,7 +2687,7 @@
       </c>
       <c r="AI15" s="9" t="n"/>
       <c r="AJ15" s="5" t="n">
-        <v>77</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16">
@@ -2730,7 +2728,7 @@
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="K16" s="4" t="n"/>
@@ -2758,13 +2756,13 @@
         <v>1</v>
       </c>
       <c r="T16" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="U16" s="8" t="n">
-        <v>340.07</v>
+        <v>883.59</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>44.16</v>
+        <v>115.04</v>
       </c>
       <c r="W16" s="6" t="inlineStr">
         <is>
@@ -2772,7 +2770,7 @@
         </is>
       </c>
       <c r="X16" s="8" t="n">
-        <v>12.04</v>
+        <v>31.35</v>
       </c>
       <c r="Y16" s="5" t="n">
         <v>148</v>
@@ -2810,7 +2808,7 @@
       </c>
       <c r="AI16" s="9" t="n"/>
       <c r="AJ16" s="5" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17">
@@ -2822,21 +2820,21 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="4" t="n"/>
       <c r="D17" s="5" t="n">
-        <v>554160609</v>
+        <v>552857208</v>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>HF329719904</t>
+          <t>HF419012518</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>03/27/2026</t>
+          <t>03/13/2026</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
+          <t>ChampVA - HAC</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -2846,7 +2844,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
+          <t>ChampVA - HAC</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
@@ -2860,7 +2858,7 @@
         <v/>
       </c>
       <c r="M17" s="7" t="n">
-        <v>46473</v>
+        <v>46459</v>
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
@@ -2882,36 +2880,36 @@
         <v>396.27</v>
       </c>
       <c r="U17" s="8" t="n">
-        <v>340.19</v>
+        <v>340.07</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>44.04</v>
+        <v>44.16</v>
       </c>
       <c r="W17" s="6" t="inlineStr">
         <is>
-          <t>04/22/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="X17" s="8" t="n">
         <v>12.04</v>
       </c>
       <c r="Y17" s="5" t="n">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="Z17" s="6" t="inlineStr">
         <is>
-          <t>F32A</t>
+          <t>F4320</t>
         </is>
       </c>
       <c r="AA17" s="6" t="n"/>
       <c r="AB17" s="6" t="n"/>
       <c r="AC17" s="6" t="n"/>
       <c r="AD17" s="5" t="n">
-        <v>559120425</v>
+        <v>559120090</v>
       </c>
       <c r="AE17" s="6" t="inlineStr">
         <is>
-          <t>BURGHER, ABRAM</t>
+          <t>O'NEIL, ROY</t>
         </is>
       </c>
       <c r="AF17" s="6" t="inlineStr">
@@ -2931,7 +2929,7 @@
       </c>
       <c r="AI17" s="9" t="n"/>
       <c r="AJ17" s="5" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -2972,7 +2970,7 @@
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K18" s="4" t="n"/>
@@ -3000,13 +2998,13 @@
         <v>1</v>
       </c>
       <c r="T18" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="U18" s="8" t="n">
-        <v>844.25</v>
+        <v>340.19</v>
       </c>
       <c r="V18" s="8" t="n">
-        <v>103.98</v>
+        <v>44.04</v>
       </c>
       <c r="W18" s="6" t="inlineStr">
         <is>
@@ -3014,7 +3012,7 @@
         </is>
       </c>
       <c r="X18" s="8" t="n">
-        <v>28.41</v>
+        <v>12.04</v>
       </c>
       <c r="Y18" s="5" t="n">
         <v>134</v>
@@ -3052,19 +3050,23 @@
       </c>
       <c r="AI18" s="9" t="n"/>
       <c r="AJ18" s="5" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Finalized</t>
+        </is>
+      </c>
       <c r="B19" s="3" t="n"/>
       <c r="C19" s="4" t="n"/>
       <c r="D19" s="5" t="n">
-        <v>555138984</v>
+        <v>554160609</v>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>HF444976688</t>
+          <t>HF329719904</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -3074,22 +3076,22 @@
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
+          <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
           <t>Medicare Part B Arizona *</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>Medicare Part B Arizona *</t>
-        </is>
-      </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>Mercy Care Health Plan Advantage (AHCCCS)</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="K19" s="4" t="n"/>
@@ -3117,33 +3119,39 @@
         <v>1</v>
       </c>
       <c r="T19" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="U19" s="8" t="n">
-        <v>0</v>
+        <v>844.25</v>
       </c>
       <c r="V19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" s="6" t="n"/>
+        <v>103.98</v>
+      </c>
+      <c r="W19" s="6" t="inlineStr">
+        <is>
+          <t>04/22/2026</t>
+        </is>
+      </c>
       <c r="X19" s="8" t="n">
-        <v>396.27</v>
+        <v>28.41</v>
       </c>
       <c r="Y19" s="5" t="n">
         <v>134</v>
       </c>
       <c r="Z19" s="6" t="inlineStr">
         <is>
-          <t>F4320</t>
+          <t>F32A</t>
         </is>
       </c>
       <c r="AA19" s="6" t="n"/>
       <c r="AB19" s="6" t="n"/>
       <c r="AC19" s="6" t="n"/>
-      <c r="AD19" s="5" t="n"/>
+      <c r="AD19" s="5" t="n">
+        <v>559120425</v>
+      </c>
       <c r="AE19" s="6" t="inlineStr">
         <is>
-          <t>HUERTA, KARLA</t>
+          <t>BURGHER, ABRAM</t>
         </is>
       </c>
       <c r="AF19" s="6" t="inlineStr">
@@ -3163,7 +3171,7 @@
       </c>
       <c r="AI19" s="9" t="n"/>
       <c r="AJ19" s="5" t="n">
-        <v>886</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20">
@@ -3200,7 +3208,7 @@
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K20" s="4" t="n"/>
@@ -3228,7 +3236,7 @@
         <v>1</v>
       </c>
       <c r="T20" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="U20" s="8" t="n">
         <v>0</v>
@@ -3238,7 +3246,7 @@
       </c>
       <c r="W20" s="6" t="n"/>
       <c r="X20" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="Y20" s="5" t="n">
         <v>134</v>
@@ -3274,7 +3282,7 @@
       </c>
       <c r="AI20" s="9" t="n"/>
       <c r="AJ20" s="5" t="n">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="21">
@@ -3282,16 +3290,16 @@
       <c r="B21" s="3" t="n"/>
       <c r="C21" s="4" t="n"/>
       <c r="D21" s="5" t="n">
-        <v>554403926</v>
+        <v>555138984</v>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>HF550289743</t>
+          <t>HF444976688</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>03/30/2026</t>
+          <t>03/27/2026</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
@@ -3306,12 +3314,12 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>Banner Medicare Advantage Prime HMO (BMAH)</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="K21" s="4" t="n"/>
@@ -3320,7 +3328,7 @@
         <v/>
       </c>
       <c r="M21" s="7" t="n">
-        <v>46476</v>
+        <v>46473</v>
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
@@ -3339,7 +3347,7 @@
         <v>1</v>
       </c>
       <c r="T21" s="8" t="n">
-        <v>1029.98</v>
+        <v>976.64</v>
       </c>
       <c r="U21" s="8" t="n">
         <v>0</v>
@@ -3347,20 +3355,16 @@
       <c r="V21" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="W21" s="6" t="inlineStr">
-        <is>
-          <t>04/13/2026</t>
-        </is>
-      </c>
+      <c r="W21" s="6" t="n"/>
       <c r="X21" s="8" t="n">
-        <v>1029.98</v>
+        <v>976.64</v>
       </c>
       <c r="Y21" s="5" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="Z21" s="6" t="inlineStr">
         <is>
-          <t>F1190</t>
+          <t>F4320</t>
         </is>
       </c>
       <c r="AA21" s="6" t="n"/>
@@ -3369,12 +3373,12 @@
       <c r="AD21" s="5" t="n"/>
       <c r="AE21" s="6" t="inlineStr">
         <is>
-          <t>KALLGREN, MARK</t>
+          <t>HUERTA, KARLA</t>
         </is>
       </c>
       <c r="AF21" s="6" t="inlineStr">
         <is>
-          <t>ASAP Peoria</t>
+          <t>ASAP - DEER VALLEY</t>
         </is>
       </c>
       <c r="AG21" s="6" t="inlineStr">
@@ -3389,7 +3393,7 @@
       </c>
       <c r="AI21" s="9" t="n"/>
       <c r="AJ21" s="5" t="n">
-        <v>257</v>
+        <v>887</v>
       </c>
     </row>
     <row r="22">
@@ -3426,7 +3430,7 @@
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="K22" s="4" t="n"/>
@@ -3454,7 +3458,7 @@
         <v>1</v>
       </c>
       <c r="T22" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="U22" s="8" t="n">
         <v>0</v>
@@ -3468,7 +3472,7 @@
         </is>
       </c>
       <c r="X22" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="Y22" s="5" t="n">
         <v>131</v>
@@ -3504,7 +3508,7 @@
       </c>
       <c r="AI22" s="9" t="n"/>
       <c r="AJ22" s="5" t="n">
-        <v>264</v>
+        <v>257</v>
       </c>
     </row>
     <row r="23">
@@ -3512,36 +3516,36 @@
       <c r="B23" s="3" t="n"/>
       <c r="C23" s="4" t="n"/>
       <c r="D23" s="5" t="n">
-        <v>566722180</v>
+        <v>554403926</v>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>HF537685966</t>
+          <t>HF550289743</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>03/30/2026</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>Medicare Part B Arizona *</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>Medicare Part B Arizona *</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>Medicare Part B Arizona *</t>
+          <t>Banner Medicare Advantage Prime HMO (BMAH)</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K23" s="4" t="n"/>
@@ -3550,16 +3554,16 @@
         <v/>
       </c>
       <c r="M23" s="7" t="n">
-        <v>46175</v>
+        <v>46476</v>
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
-          <t>90 days</t>
+          <t>365 days</t>
         </is>
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
-          <t>BCBS</t>
+          <t>MEDICARE</t>
         </is>
       </c>
       <c r="P23" s="6" t="n"/>
@@ -3569,7 +3573,7 @@
         <v>1</v>
       </c>
       <c r="T23" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="U23" s="8" t="n">
         <v>0</v>
@@ -3579,18 +3583,18 @@
       </c>
       <c r="W23" s="6" t="inlineStr">
         <is>
-          <t>04/22/2026</t>
+          <t>04/13/2026</t>
         </is>
       </c>
       <c r="X23" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="Y23" s="5" t="n">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="Z23" s="6" t="inlineStr">
         <is>
-          <t>F330</t>
+          <t>F1190</t>
         </is>
       </c>
       <c r="AA23" s="6" t="n"/>
@@ -3599,12 +3603,12 @@
       <c r="AD23" s="5" t="n"/>
       <c r="AE23" s="6" t="inlineStr">
         <is>
-          <t>BAUGHER, TIMOTHY</t>
+          <t>KALLGREN, MARK</t>
         </is>
       </c>
       <c r="AF23" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP Peoria</t>
         </is>
       </c>
       <c r="AG23" s="6" t="inlineStr">
@@ -3617,13 +3621,9 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI23" s="9" t="inlineStr">
-        <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
-        </is>
-      </c>
+      <c r="AI23" s="9" t="n"/>
       <c r="AJ23" s="5" t="n">
-        <v>909</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="K24" s="4" t="n"/>
@@ -3685,10 +3685,10 @@
       <c r="Q24" s="6" t="n"/>
       <c r="R24" s="6" t="n"/>
       <c r="S24" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T24" s="8" t="n">
-        <v>792.54</v>
+        <v>976.64</v>
       </c>
       <c r="U24" s="8" t="n">
         <v>0</v>
@@ -3702,7 +3702,7 @@
         </is>
       </c>
       <c r="X24" s="8" t="n">
-        <v>792.54</v>
+        <v>976.64</v>
       </c>
       <c r="Y24" s="5" t="n">
         <v>157</v>
@@ -3738,11 +3738,11 @@
       </c>
       <c r="AI24" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ24" s="5" t="n">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="25">
@@ -3750,36 +3750,36 @@
       <c r="B25" s="3" t="n"/>
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="5" t="n">
-        <v>551769931</v>
+        <v>566722180</v>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>HF372010397</t>
+          <t>HF537685966</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>No Payer</t>
+          <t>Medicare Part B Arizona *</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K25" s="4" t="n"/>
@@ -3788,7 +3788,7 @@
         <v/>
       </c>
       <c r="M25" s="7" t="n">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
@@ -3797,17 +3797,17 @@
       </c>
       <c r="O25" s="6" t="inlineStr">
         <is>
-          <t>OPTUM</t>
+          <t>BCBS</t>
         </is>
       </c>
       <c r="P25" s="6" t="n"/>
       <c r="Q25" s="6" t="n"/>
       <c r="R25" s="6" t="n"/>
       <c r="S25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T25" s="8" t="n">
-        <v>976.64</v>
+        <v>792.54</v>
       </c>
       <c r="U25" s="8" t="n">
         <v>0</v>
@@ -3817,18 +3817,18 @@
       </c>
       <c r="W25" s="6" t="inlineStr">
         <is>
-          <t>04/29/2026</t>
+          <t>04/22/2026</t>
         </is>
       </c>
       <c r="X25" s="8" t="n">
-        <v>976.64</v>
+        <v>792.54</v>
       </c>
       <c r="Y25" s="5" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Z25" s="6" t="inlineStr">
         <is>
-          <t>F1190</t>
+          <t>F330</t>
         </is>
       </c>
       <c r="AA25" s="6" t="n"/>
@@ -3837,12 +3837,12 @@
       <c r="AD25" s="5" t="n"/>
       <c r="AE25" s="6" t="inlineStr">
         <is>
-          <t>LEATHEM, JARRETT</t>
+          <t>BAUGHER, TIMOTHY</t>
         </is>
       </c>
       <c r="AF25" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG25" s="6" t="inlineStr">
@@ -3855,9 +3855,13 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI25" s="9" t="n"/>
+      <c r="AI25" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
+        </is>
+      </c>
       <c r="AJ25" s="5" t="n">
-        <v>757</v>
+        <v>910</v>
       </c>
     </row>
     <row r="26">
@@ -3894,7 +3898,7 @@
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="K26" s="4" t="n"/>
@@ -3922,7 +3926,7 @@
         <v>1</v>
       </c>
       <c r="T26" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="U26" s="8" t="n">
         <v>0</v>
@@ -3936,7 +3940,7 @@
         </is>
       </c>
       <c r="X26" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="Y26" s="5" t="n">
         <v>156</v>
@@ -3972,48 +3976,44 @@
       </c>
       <c r="AI26" s="9" t="n"/>
       <c r="AJ26" s="5" t="n">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="n"/>
       <c r="B27" s="3" t="n"/>
       <c r="C27" s="4" t="n"/>
       <c r="D27" s="5" t="n">
-        <v>551830492</v>
+        <v>551769931</v>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>HF417864409</t>
+          <t>HF372010397</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>United Healthcare</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
+          <t>No Payer</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K27" s="4" t="n"/>
@@ -4022,7 +4022,7 @@
         <v/>
       </c>
       <c r="M27" s="7" t="n">
-        <v>46177</v>
+        <v>46176</v>
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
-          <t>UHC COMMERCIAL</t>
+          <t>OPTUM</t>
         </is>
       </c>
       <c r="P27" s="6" t="n"/>
@@ -4041,36 +4041,34 @@
         <v>1</v>
       </c>
       <c r="T27" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="U27" s="8" t="n">
-        <v>886.62</v>
+        <v>0</v>
       </c>
       <c r="V27" s="8" t="n">
-        <v>250.79</v>
+        <v>0</v>
       </c>
       <c r="W27" s="6" t="inlineStr">
         <is>
-          <t>06/23/2026</t>
+          <t>04/29/2026</t>
         </is>
       </c>
       <c r="X27" s="8" t="n">
-        <v>-107.43</v>
+        <v>396.27</v>
       </c>
       <c r="Y27" s="5" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Z27" s="6" t="inlineStr">
         <is>
-          <t>F39</t>
+          <t>F1190</t>
         </is>
       </c>
       <c r="AA27" s="6" t="n"/>
       <c r="AB27" s="6" t="n"/>
       <c r="AC27" s="6" t="n"/>
-      <c r="AD27" s="5" t="n">
-        <v>560056768</v>
-      </c>
+      <c r="AD27" s="5" t="n"/>
       <c r="AE27" s="6" t="inlineStr">
         <is>
           <t>LEATHEM, JARRETT</t>
@@ -4078,7 +4076,7 @@
       </c>
       <c r="AF27" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - DEER VALLEY</t>
         </is>
       </c>
       <c r="AG27" s="6" t="inlineStr">
@@ -4093,7 +4091,7 @@
       </c>
       <c r="AI27" s="9" t="n"/>
       <c r="AJ27" s="5" t="n">
-        <v>261</v>
+        <v>758</v>
       </c>
     </row>
     <row r="28">
@@ -4134,7 +4132,7 @@
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="K28" s="4" t="n"/>
@@ -4162,13 +4160,13 @@
         <v>1</v>
       </c>
       <c r="T28" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="U28" s="8" t="n">
-        <v>337.07</v>
+        <v>886.62</v>
       </c>
       <c r="V28" s="8" t="n">
-        <v>104.01</v>
+        <v>250.79</v>
       </c>
       <c r="W28" s="6" t="inlineStr">
         <is>
@@ -4176,7 +4174,7 @@
         </is>
       </c>
       <c r="X28" s="8" t="n">
-        <v>-44.81</v>
+        <v>-107.43</v>
       </c>
       <c r="Y28" s="5" t="n">
         <v>155</v>
@@ -4214,19 +4212,23 @@
       </c>
       <c r="AI28" s="9" t="n"/>
       <c r="AJ28" s="5" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
       <c r="B29" s="3" t="n"/>
       <c r="C29" s="4" t="n"/>
       <c r="D29" s="5" t="n">
-        <v>551874008</v>
+        <v>551830492</v>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>HF515864933</t>
+          <t>HF417864409</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -4236,17 +4238,17 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>United Healthcare</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>No Payer</t>
+          <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
@@ -4269,7 +4271,7 @@
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>OPTUM</t>
+          <t>UHC COMMERCIAL</t>
         </is>
       </c>
       <c r="P29" s="6" t="n"/>
@@ -4282,39 +4284,41 @@
         <v>396.27</v>
       </c>
       <c r="U29" s="8" t="n">
-        <v>0</v>
+        <v>337.07</v>
       </c>
       <c r="V29" s="8" t="n">
-        <v>0</v>
+        <v>104.01</v>
       </c>
       <c r="W29" s="6" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>06/23/2026</t>
         </is>
       </c>
       <c r="X29" s="8" t="n">
-        <v>396.27</v>
+        <v>-44.81</v>
       </c>
       <c r="Y29" s="5" t="n">
         <v>155</v>
       </c>
       <c r="Z29" s="6" t="inlineStr">
         <is>
-          <t>F4320</t>
+          <t>F39</t>
         </is>
       </c>
       <c r="AA29" s="6" t="n"/>
       <c r="AB29" s="6" t="n"/>
       <c r="AC29" s="6" t="n"/>
-      <c r="AD29" s="5" t="n"/>
+      <c r="AD29" s="5" t="n">
+        <v>560056768</v>
+      </c>
       <c r="AE29" s="6" t="inlineStr">
         <is>
-          <t>KRAUSE, JEFFREY</t>
+          <t>LEATHEM, JARRETT</t>
         </is>
       </c>
       <c r="AF29" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG29" s="6" t="inlineStr">
@@ -4329,7 +4333,7 @@
       </c>
       <c r="AI29" s="9" t="n"/>
       <c r="AJ29" s="5" t="n">
-        <v>450</v>
+        <v>262</v>
       </c>
     </row>
     <row r="30">
@@ -4366,7 +4370,7 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K30" s="4" t="n"/>
@@ -4394,7 +4398,7 @@
         <v>1</v>
       </c>
       <c r="T30" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="U30" s="8" t="n">
         <v>0</v>
@@ -4408,7 +4412,7 @@
         </is>
       </c>
       <c r="X30" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="Y30" s="5" t="n">
         <v>155</v>
@@ -4444,7 +4448,7 @@
       </c>
       <c r="AI30" s="9" t="n"/>
       <c r="AJ30" s="5" t="n">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="31">
@@ -4452,16 +4456,16 @@
       <c r="B31" s="3" t="n"/>
       <c r="C31" s="4" t="n"/>
       <c r="D31" s="5" t="n">
-        <v>552405449</v>
+        <v>551874008</v>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>HF509386349</t>
+          <t>HF515864933</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>03/11/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
@@ -4490,7 +4494,7 @@
         <v/>
       </c>
       <c r="M31" s="7" t="n">
-        <v>46182</v>
+        <v>46177</v>
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
@@ -4526,11 +4530,11 @@
         <v>1029.98</v>
       </c>
       <c r="Y31" s="5" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="Z31" s="6" t="inlineStr">
         <is>
-          <t>F1190</t>
+          <t>F4320</t>
         </is>
       </c>
       <c r="AA31" s="6" t="n"/>
@@ -4539,7 +4543,7 @@
       <c r="AD31" s="5" t="n"/>
       <c r="AE31" s="6" t="inlineStr">
         <is>
-          <t>O'NEIL, ROY</t>
+          <t>KRAUSE, JEFFREY</t>
         </is>
       </c>
       <c r="AF31" s="6" t="inlineStr">
@@ -4559,7 +4563,7 @@
       </c>
       <c r="AI31" s="9" t="n"/>
       <c r="AJ31" s="5" t="n">
-        <v>89</v>
+        <v>451</v>
       </c>
     </row>
     <row r="32">
@@ -4596,7 +4600,7 @@
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="K32" s="4" t="n"/>
@@ -4624,7 +4628,7 @@
         <v>1</v>
       </c>
       <c r="T32" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="U32" s="8" t="n">
         <v>0</v>
@@ -4638,7 +4642,7 @@
         </is>
       </c>
       <c r="X32" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="Y32" s="5" t="n">
         <v>150</v>
@@ -4674,7 +4678,7 @@
       </c>
       <c r="AI32" s="9" t="n"/>
       <c r="AJ32" s="5" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33">
@@ -4682,26 +4686,26 @@
       <c r="B33" s="3" t="n"/>
       <c r="C33" s="4" t="n"/>
       <c r="D33" s="5" t="n">
-        <v>563362999</v>
+        <v>552405449</v>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>HF499452983</t>
+          <t>HF509386349</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>03/13/2026</t>
+          <t>03/11/2026</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
@@ -4711,7 +4715,7 @@
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K33" s="4" t="n"/>
@@ -4720,7 +4724,7 @@
         <v/>
       </c>
       <c r="M33" s="7" t="n">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
@@ -4729,21 +4733,17 @@
       </c>
       <c r="O33" s="6" t="inlineStr">
         <is>
-          <t>UHC COMMUNITY</t>
-        </is>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
+          <t>OPTUM</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="n"/>
       <c r="Q33" s="6" t="n"/>
       <c r="R33" s="6" t="n"/>
       <c r="S33" s="5" t="n">
         <v>1</v>
       </c>
       <c r="T33" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="U33" s="8" t="n">
         <v>0</v>
@@ -4753,18 +4753,18 @@
       </c>
       <c r="W33" s="6" t="inlineStr">
         <is>
-          <t>07/20/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="X33" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="Y33" s="5" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Z33" s="6" t="inlineStr">
         <is>
-          <t>F39</t>
+          <t>F1190</t>
         </is>
       </c>
       <c r="AA33" s="6" t="n"/>
@@ -4773,12 +4773,12 @@
       <c r="AD33" s="5" t="n"/>
       <c r="AE33" s="6" t="inlineStr">
         <is>
-          <t>KALLGREN, MARK</t>
+          <t>O'NEIL, ROY</t>
         </is>
       </c>
       <c r="AF33" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - DEER VALLEY</t>
         </is>
       </c>
       <c r="AG33" s="6" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="AI33" s="9" t="n"/>
       <c r="AJ33" s="5" t="n">
-        <v>411</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="K34" s="4" t="n"/>
@@ -4851,14 +4851,18 @@
           <t>UHC COMMUNITY</t>
         </is>
       </c>
-      <c r="P34" s="6" t="n"/>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="Q34" s="6" t="n"/>
       <c r="R34" s="6" t="n"/>
       <c r="S34" s="5" t="n">
         <v>1</v>
       </c>
       <c r="T34" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="U34" s="8" t="n">
         <v>0</v>
@@ -4872,7 +4876,7 @@
         </is>
       </c>
       <c r="X34" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="Y34" s="5" t="n">
         <v>148</v>
@@ -4908,7 +4912,7 @@
       </c>
       <c r="AI34" s="9" t="n"/>
       <c r="AJ34" s="5" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="35">
@@ -4916,31 +4920,31 @@
       <c r="B35" s="3" t="n"/>
       <c r="C35" s="4" t="n"/>
       <c r="D35" s="5" t="n">
-        <v>552859864</v>
+        <v>563362999</v>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>HF492208813</t>
+          <t>HF499452983</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>03/16/2026</t>
+          <t>03/13/2026</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>No Payer</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
@@ -4954,7 +4958,7 @@
         <v/>
       </c>
       <c r="M35" s="7" t="n">
-        <v>46187</v>
+        <v>46184</v>
       </c>
       <c r="N35" s="6" t="inlineStr">
         <is>
@@ -4963,7 +4967,7 @@
       </c>
       <c r="O35" s="6" t="inlineStr">
         <is>
-          <t>BCBS</t>
+          <t>UHC COMMUNITY</t>
         </is>
       </c>
       <c r="P35" s="6" t="n"/>
@@ -4983,36 +4987,32 @@
       </c>
       <c r="W35" s="6" t="inlineStr">
         <is>
-          <t>04/23/2026</t>
+          <t>07/20/2026</t>
         </is>
       </c>
       <c r="X35" s="8" t="n">
         <v>396.27</v>
       </c>
       <c r="Y35" s="5" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Z35" s="6" t="inlineStr">
         <is>
-          <t>F1190</t>
-        </is>
-      </c>
-      <c r="AA35" s="6" t="inlineStr">
-        <is>
-          <t>F411</t>
-        </is>
-      </c>
+          <t>F39</t>
+        </is>
+      </c>
+      <c r="AA35" s="6" t="n"/>
       <c r="AB35" s="6" t="n"/>
       <c r="AC35" s="6" t="n"/>
       <c r="AD35" s="5" t="n"/>
       <c r="AE35" s="6" t="inlineStr">
         <is>
-          <t>MEARS, CHAD</t>
+          <t>KALLGREN, MARK</t>
         </is>
       </c>
       <c r="AF35" s="6" t="inlineStr">
         <is>
-          <t>ASAP Peoria</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG35" s="6" t="inlineStr">
@@ -5025,13 +5025,9 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI35" s="9" t="inlineStr">
-        <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
-        </is>
-      </c>
+      <c r="AI35" s="9" t="n"/>
       <c r="AJ35" s="5" t="n">
-        <v>760</v>
+        <v>412</v>
       </c>
     </row>
     <row r="36">
@@ -5068,7 +5064,7 @@
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K36" s="4" t="n"/>
@@ -5096,7 +5092,7 @@
         <v>1</v>
       </c>
       <c r="T36" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="U36" s="8" t="n">
         <v>0</v>
@@ -5110,7 +5106,7 @@
         </is>
       </c>
       <c r="X36" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="Y36" s="5" t="n">
         <v>145</v>
@@ -5150,11 +5146,11 @@
       </c>
       <c r="AI36" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ36" s="5" t="n">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="37">
@@ -5162,31 +5158,31 @@
       <c r="B37" s="3" t="n"/>
       <c r="C37" s="4" t="n"/>
       <c r="D37" s="5" t="n">
-        <v>553133483</v>
+        <v>552859864</v>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>HF542079660</t>
+          <t>HF492208813</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>03/18/2026</t>
+          <t>03/16/2026</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>United Healthcare</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>United Healthcare</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>No Payer</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
@@ -5200,7 +5196,7 @@
         <v/>
       </c>
       <c r="M37" s="7" t="n">
-        <v>46189</v>
+        <v>46187</v>
       </c>
       <c r="N37" s="6" t="inlineStr">
         <is>
@@ -5209,7 +5205,7 @@
       </c>
       <c r="O37" s="6" t="inlineStr">
         <is>
-          <t>UHC COMMERCIAL</t>
+          <t>BCBS</t>
         </is>
       </c>
       <c r="P37" s="6" t="n"/>
@@ -5229,32 +5225,36 @@
       </c>
       <c r="W37" s="6" t="inlineStr">
         <is>
-          <t>05/19/2026</t>
+          <t>04/23/2026</t>
         </is>
       </c>
       <c r="X37" s="8" t="n">
         <v>1029.98</v>
       </c>
       <c r="Y37" s="5" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Z37" s="6" t="inlineStr">
         <is>
-          <t>F39</t>
-        </is>
-      </c>
-      <c r="AA37" s="6" t="n"/>
+          <t>F1190</t>
+        </is>
+      </c>
+      <c r="AA37" s="6" t="inlineStr">
+        <is>
+          <t>F411</t>
+        </is>
+      </c>
       <c r="AB37" s="6" t="n"/>
       <c r="AC37" s="6" t="n"/>
       <c r="AD37" s="5" t="n"/>
       <c r="AE37" s="6" t="inlineStr">
         <is>
-          <t>O'NEIL, ROY</t>
+          <t>MEARS, CHAD</t>
         </is>
       </c>
       <c r="AF37" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP Peoria</t>
         </is>
       </c>
       <c r="AG37" s="6" t="inlineStr">
@@ -5267,9 +5267,13 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI37" s="9" t="n"/>
+      <c r="AI37" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
+        </is>
+      </c>
       <c r="AJ37" s="5" t="n">
-        <v>91</v>
+        <v>761</v>
       </c>
     </row>
     <row r="38">
@@ -5306,7 +5310,7 @@
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="K38" s="4" t="n"/>
@@ -5334,7 +5338,7 @@
         <v>1</v>
       </c>
       <c r="T38" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="U38" s="8" t="n">
         <v>0</v>
@@ -5348,7 +5352,7 @@
         </is>
       </c>
       <c r="X38" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="Y38" s="5" t="n">
         <v>143</v>
@@ -5384,7 +5388,7 @@
       </c>
       <c r="AI38" s="9" t="n"/>
       <c r="AJ38" s="5" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39">
@@ -5392,11 +5396,11 @@
       <c r="B39" s="3" t="n"/>
       <c r="C39" s="4" t="n"/>
       <c r="D39" s="5" t="n">
-        <v>553148506</v>
+        <v>553133483</v>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>HF341023592</t>
+          <t>HF542079660</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -5406,12 +5410,12 @@
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>United Healthcare</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>United Healthcare</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
@@ -5421,7 +5425,7 @@
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K39" s="4" t="n"/>
@@ -5439,7 +5443,7 @@
       </c>
       <c r="O39" s="6" t="inlineStr">
         <is>
-          <t>OPTUM</t>
+          <t>UHC COMMERCIAL</t>
         </is>
       </c>
       <c r="P39" s="6" t="n"/>
@@ -5449,7 +5453,7 @@
         <v>1</v>
       </c>
       <c r="T39" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="U39" s="8" t="n">
         <v>0</v>
@@ -5459,31 +5463,27 @@
       </c>
       <c r="W39" s="6" t="inlineStr">
         <is>
-          <t>05/25/2026</t>
+          <t>05/19/2026</t>
         </is>
       </c>
       <c r="X39" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="Y39" s="5" t="n">
         <v>143</v>
       </c>
       <c r="Z39" s="6" t="inlineStr">
         <is>
-          <t>F331</t>
-        </is>
-      </c>
-      <c r="AA39" s="6" t="inlineStr">
-        <is>
-          <t>F411</t>
-        </is>
-      </c>
+          <t>F39</t>
+        </is>
+      </c>
+      <c r="AA39" s="6" t="n"/>
       <c r="AB39" s="6" t="n"/>
       <c r="AC39" s="6" t="n"/>
       <c r="AD39" s="5" t="n"/>
       <c r="AE39" s="6" t="inlineStr">
         <is>
-          <t>TURLEY, TODD</t>
+          <t>O'NEIL, ROY</t>
         </is>
       </c>
       <c r="AF39" s="6" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="AG39" s="6" t="inlineStr">
         <is>
-          <t>05/11/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="AH39" s="6" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="AI39" s="9" t="n"/>
       <c r="AJ39" s="5" t="n">
-        <v>45</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="K40" s="4" t="n"/>
@@ -5568,7 +5568,7 @@
         <v>1</v>
       </c>
       <c r="T40" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="U40" s="8" t="n">
         <v>0</v>
@@ -5582,7 +5582,7 @@
         </is>
       </c>
       <c r="X40" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="Y40" s="5" t="n">
         <v>143</v>
@@ -5622,28 +5622,24 @@
       </c>
       <c r="AI40" s="9" t="n"/>
       <c r="AJ40" s="5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Received</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="n"/>
       <c r="B41" s="3" t="n"/>
       <c r="C41" s="4" t="n"/>
       <c r="D41" s="5" t="n">
-        <v>553362911</v>
+        <v>553148506</v>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>HF550612373</t>
+          <t>HF341023592</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>03/20/2026</t>
+          <t>03/18/2026</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
@@ -5663,7 +5659,7 @@
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K41" s="4" t="n"/>
@@ -5672,7 +5668,7 @@
         <v/>
       </c>
       <c r="M41" s="7" t="n">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="N41" s="6" t="inlineStr">
         <is>
@@ -5691,47 +5687,51 @@
         <v>1</v>
       </c>
       <c r="T41" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="U41" s="8" t="n">
-        <v>899.4</v>
+        <v>0</v>
       </c>
       <c r="V41" s="8" t="n">
-        <v>261.16</v>
+        <v>0</v>
       </c>
       <c r="W41" s="6" t="inlineStr">
         <is>
-          <t>06/12/2026</t>
+          <t>05/25/2026</t>
         </is>
       </c>
       <c r="X41" s="8" t="n">
-        <v>-130.58</v>
+        <v>396.27</v>
       </c>
       <c r="Y41" s="5" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="Z41" s="6" t="inlineStr">
         <is>
-          <t>F4320</t>
-        </is>
-      </c>
-      <c r="AA41" s="6" t="n"/>
+          <t>F331</t>
+        </is>
+      </c>
+      <c r="AA41" s="6" t="inlineStr">
+        <is>
+          <t>F411</t>
+        </is>
+      </c>
       <c r="AB41" s="6" t="n"/>
       <c r="AC41" s="6" t="n"/>
       <c r="AD41" s="5" t="n"/>
       <c r="AE41" s="6" t="inlineStr">
         <is>
-          <t>MEARS, CHAD</t>
+          <t>TURLEY, TODD</t>
         </is>
       </c>
       <c r="AF41" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG41" s="6" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>05/11/2026</t>
         </is>
       </c>
       <c r="AH41" s="6" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="AI41" s="9" t="n"/>
       <c r="AJ41" s="5" t="n">
-        <v>656</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="K42" s="4" t="n"/>
@@ -5810,13 +5810,13 @@
         <v>1</v>
       </c>
       <c r="T42" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="U42" s="8" t="n">
-        <v>346.14</v>
+        <v>899.4</v>
       </c>
       <c r="V42" s="8" t="n">
-        <v>100.26</v>
+        <v>261.16</v>
       </c>
       <c r="W42" s="6" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         </is>
       </c>
       <c r="X42" s="8" t="n">
-        <v>-50.13</v>
+        <v>-130.58</v>
       </c>
       <c r="Y42" s="5" t="n">
         <v>141</v>
@@ -5860,19 +5860,23 @@
       </c>
       <c r="AI42" s="9" t="n"/>
       <c r="AJ42" s="5" t="n">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n"/>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Received</t>
+        </is>
+      </c>
       <c r="B43" s="3" t="n"/>
       <c r="C43" s="4" t="n"/>
       <c r="D43" s="5" t="n">
-        <v>553498942</v>
+        <v>553362911</v>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>HF549281205</t>
+          <t>HF550612373</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -5882,12 +5886,12 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -5915,7 +5919,7 @@
       </c>
       <c r="O43" s="6" t="inlineStr">
         <is>
-          <t>BCBS</t>
+          <t>OPTUM</t>
         </is>
       </c>
       <c r="P43" s="6" t="n"/>
@@ -5928,18 +5932,18 @@
         <v>396.27</v>
       </c>
       <c r="U43" s="8" t="n">
-        <v>0</v>
+        <v>346.14</v>
       </c>
       <c r="V43" s="8" t="n">
-        <v>0</v>
+        <v>100.26</v>
       </c>
       <c r="W43" s="6" t="inlineStr">
         <is>
-          <t>04/12/2026</t>
+          <t>06/12/2026</t>
         </is>
       </c>
       <c r="X43" s="8" t="n">
-        <v>396.27</v>
+        <v>-50.13</v>
       </c>
       <c r="Y43" s="5" t="n">
         <v>141</v>
@@ -5955,7 +5959,7 @@
       <c r="AD43" s="5" t="n"/>
       <c r="AE43" s="6" t="inlineStr">
         <is>
-          <t>MORALES, DAVID</t>
+          <t>MEARS, CHAD</t>
         </is>
       </c>
       <c r="AF43" s="6" t="inlineStr">
@@ -5973,13 +5977,9 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI43" s="9" t="inlineStr">
-        <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
-        </is>
-      </c>
+      <c r="AI43" s="9" t="n"/>
       <c r="AJ43" s="5" t="n">
-        <v>93</v>
+        <v>657</v>
       </c>
     </row>
     <row r="44">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K44" s="4" t="n"/>
@@ -6044,7 +6044,7 @@
         <v>1</v>
       </c>
       <c r="T44" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="U44" s="8" t="n">
         <v>0</v>
@@ -6058,7 +6058,7 @@
         </is>
       </c>
       <c r="X44" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="Y44" s="5" t="n">
         <v>141</v>
@@ -6094,11 +6094,11 @@
       </c>
       <c r="AI44" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ44" s="5" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45">
@@ -6106,26 +6106,26 @@
       <c r="B45" s="3" t="n"/>
       <c r="C45" s="4" t="n"/>
       <c r="D45" s="5" t="n">
-        <v>555169750</v>
+        <v>553498942</v>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>HF341023592</t>
+          <t>HF549281205</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>03/23/2026</t>
+          <t>03/20/2026</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>Blue Cross Blue Shield of Arizona (BCBS AZ)</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="K45" s="4" t="n"/>
@@ -6144,7 +6144,7 @@
         <v/>
       </c>
       <c r="M45" s="7" t="n">
-        <v>46194</v>
+        <v>46191</v>
       </c>
       <c r="N45" s="6" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
       </c>
       <c r="O45" s="6" t="inlineStr">
         <is>
-          <t>OPTUM</t>
+          <t>BCBS</t>
         </is>
       </c>
       <c r="P45" s="6" t="n"/>
@@ -6163,7 +6163,7 @@
         <v>1</v>
       </c>
       <c r="T45" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="U45" s="8" t="n">
         <v>0</v>
@@ -6173,41 +6173,37 @@
       </c>
       <c r="W45" s="6" t="inlineStr">
         <is>
-          <t>04/29/2026</t>
+          <t>04/12/2026</t>
         </is>
       </c>
       <c r="X45" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="Y45" s="5" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="Z45" s="6" t="inlineStr">
         <is>
-          <t>M5417</t>
-        </is>
-      </c>
-      <c r="AA45" s="6" t="inlineStr">
-        <is>
-          <t>Z79891</t>
-        </is>
-      </c>
+          <t>F4320</t>
+        </is>
+      </c>
+      <c r="AA45" s="6" t="n"/>
       <c r="AB45" s="6" t="n"/>
       <c r="AC45" s="6" t="n"/>
       <c r="AD45" s="5" t="n"/>
       <c r="AE45" s="6" t="inlineStr">
         <is>
-          <t>TURLEY, TODD</t>
+          <t>MORALES, DAVID</t>
         </is>
       </c>
       <c r="AF45" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Biltmore</t>
+          <t>ASAP - DEER VALLEY</t>
         </is>
       </c>
       <c r="AG45" s="6" t="inlineStr">
         <is>
-          <t>03/24/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="AH45" s="6" t="inlineStr">
@@ -6215,50 +6211,50 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI45" s="9" t="n"/>
+      <c r="AI45" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
+        </is>
+      </c>
       <c r="AJ45" s="5" t="n">
-        <v>428</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Finalized</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="n"/>
       <c r="B46" s="3" t="n"/>
       <c r="C46" s="4" t="n"/>
       <c r="D46" s="5" t="n">
-        <v>554246495</v>
+        <v>555169750</v>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>HF545223898</t>
+          <t>HF341023592</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>03/25/2026</t>
+          <t>03/23/2026</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>ChampVA - HAC</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>Humana Gold Plus HMO</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>ChampVA - HAC</t>
+          <t>No Payer</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K46" s="4" t="n"/>
@@ -6267,7 +6263,7 @@
         <v/>
       </c>
       <c r="M46" s="7" t="n">
-        <v>46196</v>
+        <v>46194</v>
       </c>
       <c r="N46" s="6" t="inlineStr">
         <is>
@@ -6276,7 +6272,7 @@
       </c>
       <c r="O46" s="6" t="inlineStr">
         <is>
-          <t>HUMANA MA</t>
+          <t>OPTUM</t>
         </is>
       </c>
       <c r="P46" s="6" t="n"/>
@@ -6286,49 +6282,51 @@
         <v>1</v>
       </c>
       <c r="T46" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="U46" s="8" t="n">
-        <v>883.53</v>
+        <v>0</v>
       </c>
       <c r="V46" s="8" t="n">
-        <v>121.45</v>
+        <v>0</v>
       </c>
       <c r="W46" s="6" t="inlineStr">
         <is>
-          <t>04/11/2026</t>
+          <t>04/29/2026</t>
         </is>
       </c>
       <c r="X46" s="8" t="n">
-        <v>25</v>
+        <v>396.27</v>
       </c>
       <c r="Y46" s="5" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="Z46" s="6" t="inlineStr">
         <is>
-          <t>F4323</t>
-        </is>
-      </c>
-      <c r="AA46" s="6" t="n"/>
+          <t>M5417</t>
+        </is>
+      </c>
+      <c r="AA46" s="6" t="inlineStr">
+        <is>
+          <t>Z79891</t>
+        </is>
+      </c>
       <c r="AB46" s="6" t="n"/>
       <c r="AC46" s="6" t="n"/>
-      <c r="AD46" s="5" t="n">
-        <v>557570817</v>
-      </c>
+      <c r="AD46" s="5" t="n"/>
       <c r="AE46" s="6" t="inlineStr">
         <is>
-          <t>BURGHER, ABRAM</t>
+          <t>TURLEY, TODD</t>
         </is>
       </c>
       <c r="AF46" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY</t>
+          <t>ASAP - Biltmore</t>
         </is>
       </c>
       <c r="AG46" s="6" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>03/24/2026</t>
         </is>
       </c>
       <c r="AH46" s="6" t="inlineStr">
@@ -6336,50 +6334,50 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI46" s="9" t="inlineStr">
-        <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
-        </is>
-      </c>
+      <c r="AI46" s="9" t="n"/>
       <c r="AJ46" s="5" t="n">
-        <v>2</v>
+        <v>428</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n"/>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Finalized</t>
+        </is>
+      </c>
       <c r="B47" s="3" t="n"/>
       <c r="C47" s="4" t="n"/>
       <c r="D47" s="5" t="n">
-        <v>554088972</v>
+        <v>554246495</v>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>HF443112560</t>
+          <t>HF545223898</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>03/27/2026</t>
+          <t>03/25/2026</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>ChampVA - HAC</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
+          <t>Humana Gold Plus HMO</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>No Payer</t>
+          <t>ChampVA - HAC</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="K47" s="4" t="n"/>
@@ -6388,7 +6386,7 @@
         <v/>
       </c>
       <c r="M47" s="7" t="n">
-        <v>46198</v>
+        <v>46196</v>
       </c>
       <c r="N47" s="6" t="inlineStr">
         <is>
@@ -6397,7 +6395,7 @@
       </c>
       <c r="O47" s="6" t="inlineStr">
         <is>
-          <t>OPTUM</t>
+          <t>HUMANA MA</t>
         </is>
       </c>
       <c r="P47" s="6" t="n"/>
@@ -6407,42 +6405,44 @@
         <v>1</v>
       </c>
       <c r="T47" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="U47" s="8" t="n">
-        <v>0</v>
+        <v>883.53</v>
       </c>
       <c r="V47" s="8" t="n">
-        <v>0</v>
+        <v>121.45</v>
       </c>
       <c r="W47" s="6" t="inlineStr">
         <is>
-          <t>04/29/2026</t>
+          <t>04/11/2026</t>
         </is>
       </c>
       <c r="X47" s="8" t="n">
-        <v>396.27</v>
+        <v>25</v>
       </c>
       <c r="Y47" s="5" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Z47" s="6" t="inlineStr">
         <is>
-          <t>F1190</t>
+          <t>F4323</t>
         </is>
       </c>
       <c r="AA47" s="6" t="n"/>
       <c r="AB47" s="6" t="n"/>
       <c r="AC47" s="6" t="n"/>
-      <c r="AD47" s="5" t="n"/>
+      <c r="AD47" s="5" t="n">
+        <v>557570817</v>
+      </c>
       <c r="AE47" s="6" t="inlineStr">
         <is>
-          <t>LEATHEM, JARRETT</t>
+          <t>BURGHER, ABRAM</t>
         </is>
       </c>
       <c r="AF47" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - DEER VALLEY</t>
         </is>
       </c>
       <c r="AG47" s="6" t="inlineStr">
@@ -6455,9 +6455,13 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI47" s="9" t="n"/>
+      <c r="AI47" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
+        </is>
+      </c>
       <c r="AJ47" s="5" t="n">
-        <v>141</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -6494,7 +6498,7 @@
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K48" s="4" t="n"/>
@@ -6522,7 +6526,7 @@
         <v>1</v>
       </c>
       <c r="T48" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="U48" s="8" t="n">
         <v>0</v>
@@ -6536,7 +6540,7 @@
         </is>
       </c>
       <c r="X48" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="Y48" s="5" t="n">
         <v>134</v>
@@ -6572,7 +6576,7 @@
       </c>
       <c r="AI48" s="9" t="n"/>
       <c r="AJ48" s="5" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49">
@@ -6580,11 +6584,11 @@
       <c r="B49" s="3" t="n"/>
       <c r="C49" s="4" t="n"/>
       <c r="D49" s="5" t="n">
-        <v>563362114</v>
+        <v>554088972</v>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>HF481780302</t>
+          <t>HF443112560</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
@@ -6594,12 +6598,12 @@
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
+          <t>Optum Care Medical Network of Arizona, Utah, &amp; Washington (LifePrint)</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
@@ -6609,7 +6613,7 @@
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="K49" s="4" t="n"/>
@@ -6627,7 +6631,7 @@
       </c>
       <c r="O49" s="6" t="inlineStr">
         <is>
-          <t>UHC COMMUNITY</t>
+          <t>OPTUM</t>
         </is>
       </c>
       <c r="P49" s="6" t="n"/>
@@ -6637,7 +6641,7 @@
         <v>1</v>
       </c>
       <c r="T49" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="U49" s="8" t="n">
         <v>0</v>
@@ -6647,11 +6651,11 @@
       </c>
       <c r="W49" s="6" t="inlineStr">
         <is>
-          <t>06/24/2026</t>
+          <t>04/29/2026</t>
         </is>
       </c>
       <c r="X49" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="Y49" s="5" t="n">
         <v>134</v>
@@ -6687,7 +6691,7 @@
       </c>
       <c r="AI49" s="9" t="n"/>
       <c r="AJ49" s="5" t="n">
-        <v>207</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50">
@@ -6724,7 +6728,7 @@
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>99492</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K50" s="4" t="n"/>
@@ -6745,18 +6749,14 @@
           <t>UHC COMMUNITY</t>
         </is>
       </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
+      <c r="P50" s="6" t="n"/>
       <c r="Q50" s="6" t="n"/>
       <c r="R50" s="6" t="n"/>
       <c r="S50" s="5" t="n">
         <v>1</v>
       </c>
       <c r="T50" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="U50" s="8" t="n">
         <v>0</v>
@@ -6770,7 +6770,7 @@
         </is>
       </c>
       <c r="X50" s="8" t="n">
-        <v>1029.98</v>
+        <v>396.27</v>
       </c>
       <c r="Y50" s="5" t="n">
         <v>134</v>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="AI50" s="9" t="n"/>
       <c r="AJ50" s="5" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="51">
@@ -6814,26 +6814,26 @@
       <c r="B51" s="3" t="n"/>
       <c r="C51" s="4" t="n"/>
       <c r="D51" s="5" t="n">
-        <v>553283455</v>
+        <v>563362114</v>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>HF330559209</t>
+          <t>HF481780302</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>03/19/2026</t>
+          <t>03/27/2026</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>Banner Aetna</t>
+          <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>Banner Aetna</t>
+          <t>UnitedHealthcare Community Plan / Arizona Long Term Care</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
@@ -6852,19 +6852,23 @@
         <v/>
       </c>
       <c r="M51" s="7" t="n">
-        <v>46220</v>
+        <v>46198</v>
       </c>
       <c r="N51" s="6" t="inlineStr">
         <is>
-          <t>120 days</t>
+          <t>90 days</t>
         </is>
       </c>
       <c r="O51" s="6" t="inlineStr">
         <is>
-          <t>BANNER HEALTH &amp; AETNA</t>
-        </is>
-      </c>
-      <c r="P51" s="6" t="n"/>
+          <t>UHC COMMUNITY</t>
+        </is>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
       <c r="Q51" s="6" t="n"/>
       <c r="R51" s="6" t="n"/>
       <c r="S51" s="5" t="n">
@@ -6881,18 +6885,18 @@
       </c>
       <c r="W51" s="6" t="inlineStr">
         <is>
-          <t>06/11/2026</t>
+          <t>06/24/2026</t>
         </is>
       </c>
       <c r="X51" s="8" t="n">
         <v>1029.98</v>
       </c>
       <c r="Y51" s="5" t="n">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="Z51" s="6" t="inlineStr">
         <is>
-          <t>F4323</t>
+          <t>F1190</t>
         </is>
       </c>
       <c r="AA51" s="6" t="n"/>
@@ -6901,12 +6905,12 @@
       <c r="AD51" s="5" t="n"/>
       <c r="AE51" s="6" t="inlineStr">
         <is>
-          <t>O'NEIL, ROY</t>
+          <t>LEATHEM, JARRETT</t>
         </is>
       </c>
       <c r="AF51" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY</t>
+          <t>ASAP - Gilbert</t>
         </is>
       </c>
       <c r="AG51" s="6" t="inlineStr">
@@ -6921,7 +6925,7 @@
       </c>
       <c r="AI51" s="9" t="n"/>
       <c r="AJ51" s="5" t="n">
-        <v>762</v>
+        <v>208</v>
       </c>
     </row>
     <row r="52">
@@ -6958,7 +6962,7 @@
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99492</t>
         </is>
       </c>
       <c r="K52" s="4" t="n"/>
@@ -6986,7 +6990,7 @@
         <v>1</v>
       </c>
       <c r="T52" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="U52" s="8" t="n">
         <v>0</v>
@@ -7000,7 +7004,7 @@
         </is>
       </c>
       <c r="X52" s="8" t="n">
-        <v>396.27</v>
+        <v>1029.98</v>
       </c>
       <c r="Y52" s="5" t="n">
         <v>142</v>
@@ -7036,7 +7040,7 @@
       </c>
       <c r="AI52" s="9" t="n"/>
       <c r="AJ52" s="5" t="n">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="53">
@@ -7044,26 +7048,26 @@
       <c r="B53" s="3" t="n"/>
       <c r="C53" s="4" t="n"/>
       <c r="D53" s="5" t="n">
-        <v>553124954</v>
+        <v>553283455</v>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>HF539993491</t>
+          <t>HF330559209</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>03/18/2026</t>
+          <t>03/19/2026</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>Alignment Health Care</t>
+          <t>Banner Aetna</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>Alignment Health Care</t>
+          <t>Banner Aetna</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr">
@@ -7073,7 +7077,7 @@
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K53" s="4" t="n"/>
@@ -7081,11 +7085,17 @@
         <f>IF($M53="","",$M53-TODAY())</f>
         <v/>
       </c>
-      <c r="M53" s="7" t="n"/>
-      <c r="N53" s="6" t="n"/>
+      <c r="M53" s="7" t="n">
+        <v>46220</v>
+      </c>
+      <c r="N53" s="6" t="inlineStr">
+        <is>
+          <t>120 days</t>
+        </is>
+      </c>
       <c r="O53" s="6" t="inlineStr">
         <is>
-          <t>Not on reference list</t>
+          <t>BANNER HEALTH &amp; AETNA</t>
         </is>
       </c>
       <c r="P53" s="6" t="n"/>
@@ -7095,7 +7105,7 @@
         <v>1</v>
       </c>
       <c r="T53" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="U53" s="8" t="n">
         <v>0</v>
@@ -7105,18 +7115,18 @@
       </c>
       <c r="W53" s="6" t="inlineStr">
         <is>
-          <t>04/16/2026</t>
+          <t>06/11/2026</t>
         </is>
       </c>
       <c r="X53" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="Y53" s="5" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Z53" s="6" t="inlineStr">
         <is>
-          <t>F4320</t>
+          <t>F4323</t>
         </is>
       </c>
       <c r="AA53" s="6" t="n"/>
@@ -7125,7 +7135,7 @@
       <c r="AD53" s="5" t="n"/>
       <c r="AE53" s="6" t="inlineStr">
         <is>
-          <t>MORALES, DAVID</t>
+          <t>O'NEIL, ROY</t>
         </is>
       </c>
       <c r="AF53" s="6" t="inlineStr">
@@ -7143,13 +7153,9 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI53" s="9" t="inlineStr">
-        <is>
-          <t>No timely filing limit on file for this payer - confirm the limit from the contract or provider manual before working this claim.</t>
-        </is>
-      </c>
+      <c r="AI53" s="9" t="n"/>
       <c r="AJ53" s="5" t="n">
-        <v>444</v>
+        <v>763</v>
       </c>
     </row>
     <row r="54">
@@ -7157,26 +7163,26 @@
       <c r="B54" s="3" t="n"/>
       <c r="C54" s="4" t="n"/>
       <c r="D54" s="5" t="n">
-        <v>553124954</v>
+        <v>554404221</v>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>HF539993491</t>
+          <t>HF525117988</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>03/18/2026</t>
+          <t>03/31/2026</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>Alignment Health Care</t>
+          <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>Alignment Health Care</t>
+          <t>TRIWEST VA CCN CLAIMS</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr">
@@ -7186,7 +7192,7 @@
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="K54" s="4" t="n"/>
@@ -7194,11 +7200,17 @@
         <f>IF($M54="","",$M54-TODAY())</f>
         <v/>
       </c>
-      <c r="M54" s="7" t="n"/>
-      <c r="N54" s="6" t="n"/>
+      <c r="M54" s="7" t="n">
+        <v>46232</v>
+      </c>
+      <c r="N54" s="6" t="inlineStr">
+        <is>
+          <t>120 days</t>
+        </is>
+      </c>
       <c r="O54" s="6" t="inlineStr">
         <is>
-          <t>Not on reference list</t>
+          <t>TRIWEST</t>
         </is>
       </c>
       <c r="P54" s="6" t="n"/>
@@ -7208,7 +7220,7 @@
         <v>1</v>
       </c>
       <c r="T54" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="U54" s="8" t="n">
         <v>0</v>
@@ -7222,10 +7234,10 @@
         </is>
       </c>
       <c r="X54" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="Y54" s="5" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="Z54" s="6" t="inlineStr">
         <is>
@@ -7238,12 +7250,12 @@
       <c r="AD54" s="5" t="n"/>
       <c r="AE54" s="6" t="inlineStr">
         <is>
-          <t>MORALES, DAVID</t>
+          <t>LEATHEM, JARRETT</t>
         </is>
       </c>
       <c r="AF54" s="6" t="inlineStr">
         <is>
-          <t>ASAP - DEER VALLEY</t>
+          <t>ASAP Peoria</t>
         </is>
       </c>
       <c r="AG54" s="6" t="inlineStr">
@@ -7258,11 +7270,11 @@
       </c>
       <c r="AI54" s="9" t="inlineStr">
         <is>
-          <t>No timely filing limit on file for this payer - confirm the limit from the contract or provider manual before working this claim.</t>
+          <t>This payer name is on 2 carrier rows in the reference (VETERANS ADMIN (VA CCN) 180 days, and TRIWEST 120 days). The shorter TRIWEST window is applied - confirm which programme the claim belongs to before relying on the longer one.</t>
         </is>
       </c>
       <c r="AJ54" s="5" t="n">
-        <v>445</v>
+        <v>105</v>
       </c>
     </row>
     <row r="55">
@@ -7270,26 +7282,26 @@
       <c r="B55" s="3" t="n"/>
       <c r="C55" s="4" t="n"/>
       <c r="D55" s="5" t="n">
-        <v>553329086</v>
+        <v>553124954</v>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>HF524312806</t>
+          <t>HF539993491</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>03/20/2026</t>
+          <t>03/18/2026</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
+          <t>Alignment Health Care</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
+          <t>Alignment Health Care</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
@@ -7299,7 +7311,7 @@
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99493</t>
         </is>
       </c>
       <c r="K55" s="4" t="n"/>
@@ -7311,7 +7323,7 @@
       <c r="N55" s="6" t="n"/>
       <c r="O55" s="6" t="inlineStr">
         <is>
-          <t>MEDICA</t>
+          <t>Not on reference list</t>
         </is>
       </c>
       <c r="P55" s="6" t="n"/>
@@ -7321,7 +7333,7 @@
         <v>1</v>
       </c>
       <c r="T55" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="U55" s="8" t="n">
         <v>0</v>
@@ -7329,16 +7341,20 @@
       <c r="V55" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="W55" s="6" t="n"/>
+      <c r="W55" s="6" t="inlineStr">
+        <is>
+          <t>04/16/2026</t>
+        </is>
+      </c>
       <c r="X55" s="8" t="n">
-        <v>396.27</v>
+        <v>976.64</v>
       </c>
       <c r="Y55" s="5" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="Z55" s="6" t="inlineStr">
         <is>
-          <t>F411</t>
+          <t>F4320</t>
         </is>
       </c>
       <c r="AA55" s="6" t="n"/>
@@ -7347,12 +7363,12 @@
       <c r="AD55" s="5" t="n"/>
       <c r="AE55" s="6" t="inlineStr">
         <is>
-          <t>MEARS, CHAD</t>
+          <t>MORALES, DAVID</t>
         </is>
       </c>
       <c r="AF55" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - DEER VALLEY</t>
         </is>
       </c>
       <c r="AG55" s="6" t="inlineStr">
@@ -7365,9 +7381,13 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI55" s="9" t="n"/>
+      <c r="AI55" s="9" t="inlineStr">
+        <is>
+          <t>No timely filing limit on file for this payer - confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ55" s="5" t="n">
-        <v>345</v>
+        <v>444</v>
       </c>
     </row>
     <row r="56">
@@ -7375,26 +7395,26 @@
       <c r="B56" s="3" t="n"/>
       <c r="C56" s="4" t="n"/>
       <c r="D56" s="5" t="n">
-        <v>553329086</v>
+        <v>553124954</v>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>HF524312806</t>
+          <t>HF539993491</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>03/20/2026</t>
+          <t>03/18/2026</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
+          <t>Alignment Health Care</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>Medica Health Plan Solutions (Mayo Plan - CHI Health)</t>
+          <t>Alignment Health Care</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
@@ -7404,7 +7424,7 @@
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
-          <t>99493</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="K56" s="4" t="n"/>
@@ -7416,7 +7436,7 @@
       <c r="N56" s="6" t="n"/>
       <c r="O56" s="6" t="inlineStr">
         <is>
-          <t>MEDICA</t>
+          <t>Not on reference list</t>
         </is>
       </c>
       <c r="P56" s="6" t="n"/>
@@ -7426,7 +7446,7 @@
         <v>1</v>
       </c>
       <c r="T56" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="U56" s="8" t="n">
         <v>0</v>
@@ -7436,18 +7456,18 @@
       </c>
       <c r="W56" s="6" t="inlineStr">
         <is>
-          <t>04/17/2026</t>
+          <t>04/16/2026</t>
         </is>
       </c>
       <c r="X56" s="8" t="n">
-        <v>976.64</v>
+        <v>396.27</v>
       </c>
       <c r="Y56" s="5" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="Z56" s="6" t="inlineStr">
         <is>
-          <t>F411</t>
+          <t>F4320</t>
         </is>
       </c>
       <c r="AA56" s="6" t="n"/>
@@ -7456,12 +7476,12 @@
       <c r="AD56" s="5" t="n"/>
       <c r="AE56" s="6" t="inlineStr">
         <is>
-          <t>MEARS, CHAD</t>
+          <t>MORALES, DAVID</t>
         </is>
       </c>
       <c r="AF56" s="6" t="inlineStr">
         <is>
-          <t>ASAP - Gilbert</t>
+          <t>ASAP - DEER VALLEY</t>
         </is>
       </c>
       <c r="AG56" s="6" t="inlineStr">
@@ -7474,9 +7494,13 @@
           <t>BH</t>
         </is>
       </c>
-      <c r="AI56" s="9" t="n"/>
+      <c r="AI56" s="9" t="inlineStr">
+        <is>
+          <t>No timely filing limit on file for this payer - confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ56" s="5" t="n">
-        <v>346</v>
+        <v>445</v>
       </c>
     </row>
     <row r="57">
@@ -10222,7 +10246,7 @@
       </c>
       <c r="AI5" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ5" s="5" t="n">
@@ -10345,7 +10369,11 @@
           <t>GAE</t>
         </is>
       </c>
-      <c r="AI6" s="9" t="n"/>
+      <c r="AI6" s="9" t="inlineStr">
+        <is>
+          <t>UMR / WAUSAU is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ6" s="5" t="n">
         <v>95</v>
       </c>
@@ -10462,7 +10490,11 @@
           <t>GAE</t>
         </is>
       </c>
-      <c r="AI7" s="9" t="n"/>
+      <c r="AI7" s="9" t="inlineStr">
+        <is>
+          <t>UMR / WAUSAU is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ7" s="5" t="n">
         <v>103</v>
       </c>
@@ -10579,7 +10611,11 @@
           <t>GAE</t>
         </is>
       </c>
-      <c r="AI8" s="9" t="n"/>
+      <c r="AI8" s="9" t="inlineStr">
+        <is>
+          <t>UMR / WAUSAU is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ8" s="5" t="n">
         <v>111</v>
       </c>
@@ -10696,7 +10732,11 @@
           <t>GAE</t>
         </is>
       </c>
-      <c r="AI9" s="9" t="n"/>
+      <c r="AI9" s="9" t="inlineStr">
+        <is>
+          <t>UMR / WAUSAU is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ9" s="5" t="n">
         <v>112</v>
       </c>
@@ -10813,7 +10853,11 @@
           <t>GAE</t>
         </is>
       </c>
-      <c r="AI10" s="9" t="n"/>
+      <c r="AI10" s="9" t="inlineStr">
+        <is>
+          <t>UMR / WAUSAU is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ10" s="5" t="n">
         <v>113</v>
       </c>
@@ -10934,7 +10978,11 @@
           <t>GAE</t>
         </is>
       </c>
-      <c r="AI11" s="9" t="n"/>
+      <c r="AI11" s="9" t="inlineStr">
+        <is>
+          <t>UMR / WAUSAU is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ11" s="5" t="n">
         <v>114</v>
       </c>
@@ -11047,7 +11095,11 @@
           <t>GAE</t>
         </is>
       </c>
-      <c r="AI12" s="9" t="n"/>
+      <c r="AI12" s="9" t="inlineStr">
+        <is>
+          <t>UMR / WAUSAU is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ12" s="5" t="n">
         <v>115</v>
       </c>
@@ -12668,7 +12720,11 @@
           <t>ORTHO</t>
         </is>
       </c>
-      <c r="AI12" s="9" t="n"/>
+      <c r="AI12" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ12" s="5" t="n">
         <v>759</v>
       </c>
@@ -12785,7 +12841,7 @@
       </c>
       <c r="AI13" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ13" s="5" t="n">
@@ -12904,7 +12960,7 @@
       </c>
       <c r="AI14" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ14" s="5" t="n">
@@ -13023,7 +13079,7 @@
       </c>
       <c r="AI15" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ15" s="5" t="n">
@@ -13146,7 +13202,7 @@
       </c>
       <c r="AI16" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ16" s="5" t="n">
@@ -13269,7 +13325,7 @@
       </c>
       <c r="AI17" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ17" s="5" t="n">
@@ -13396,7 +13452,7 @@
       </c>
       <c r="AI18" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ18" s="5" t="n">
@@ -13519,7 +13575,7 @@
       </c>
       <c r="AI19" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ19" s="5" t="n">
@@ -13642,7 +13698,7 @@
       </c>
       <c r="AI20" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ20" s="5" t="n">
@@ -13765,7 +13821,7 @@
       </c>
       <c r="AI21" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ21" s="5" t="n">
@@ -14138,7 +14194,7 @@
       </c>
       <c r="AI24" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ24" s="5" t="n">
@@ -14273,7 +14329,7 @@
       </c>
       <c r="AI25" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ25" s="5" t="n">
@@ -14392,7 +14448,7 @@
       </c>
       <c r="AI26" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ26" s="5" t="n">
@@ -15509,7 +15565,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI8" s="9" t="n"/>
+      <c r="AI8" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ8" s="5" t="n">
         <v>658</v>
       </c>
@@ -15636,7 +15696,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI9" s="9" t="n"/>
+      <c r="AI9" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ9" s="5" t="n">
         <v>659</v>
       </c>
@@ -15757,7 +15821,7 @@
       </c>
       <c r="AI10" s="9" t="inlineStr">
         <is>
-          <t>BCBS AZ dropped from 365 to 90 days on 01/01/2026. All dates of service here are 2026, so 90 days applies.</t>
+          <t>Limit as stated: 365 days from DOS; 90 days as of 1/1/2026.</t>
         </is>
       </c>
       <c r="AJ10" s="5" t="n">
@@ -15888,7 +15952,7 @@
       </c>
       <c r="AI11" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ11" s="5" t="n">
@@ -16019,7 +16083,7 @@
       </c>
       <c r="AI12" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ12" s="5" t="n">
@@ -16150,7 +16214,7 @@
       </c>
       <c r="AI13" s="9" t="inlineStr">
         <is>
-          <t>Shorter of the two Humana limits (90 days ancillary vs 180 days physician). Confirm the rendering provider's category - if they bill as a physician the real deadline is 90 days later.</t>
+          <t>Limit as stated: 180 days from DOS (physicians); 90 days from DOS (ancillary providers).</t>
         </is>
       </c>
       <c r="AJ13" s="5" t="n">
@@ -16273,7 +16337,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI14" s="9" t="n"/>
+      <c r="AI14" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ14" s="5" t="n">
         <v>270</v>
       </c>
@@ -16392,7 +16460,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI15" s="9" t="n"/>
+      <c r="AI15" s="9" t="inlineStr">
+        <is>
+          <t>Limit as stated: 90 days from DOS.</t>
+        </is>
+      </c>
       <c r="AJ15" s="5" t="n">
         <v>821</v>
       </c>
@@ -16636,7 +16708,7 @@
       </c>
       <c r="AI17" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ17" s="5" t="n">
@@ -16759,7 +16831,7 @@
       </c>
       <c r="AI18" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ18" s="5" t="n">
@@ -17001,7 +17073,7 @@
       </c>
       <c r="AI20" s="9" t="inlineStr">
         <is>
-          <t>120 days is per our contract rather than a published Aetna policy.</t>
+          <t>Limit as stated: 120 days per contract.</t>
         </is>
       </c>
       <c r="AJ20" s="5" t="n">
@@ -17116,7 +17188,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI21" s="9" t="n"/>
+      <c r="AI21" s="9" t="inlineStr">
+        <is>
+          <t>AARP MA CHOICE / MEDICARE COMPLETE is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ21" s="5" t="n">
         <v>867</v>
       </c>
@@ -17229,7 +17305,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI22" s="9" t="n"/>
+      <c r="AI22" s="9" t="inlineStr">
+        <is>
+          <t>AARP MA CHOICE / MEDICARE COMPLETE is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ22" s="5" t="n">
         <v>868</v>
       </c>
@@ -17342,7 +17422,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="AI23" s="9" t="n"/>
+      <c r="AI23" s="9" t="inlineStr">
+        <is>
+          <t>AARP MA CHOICE / MEDICARE COMPLETE is on the reference list with no limit supplied (status: Needs research). Confirm the limit from the contract or provider manual before working this claim.</t>
+        </is>
+      </c>
       <c r="AJ23" s="5" t="n">
         <v>869</v>
       </c>
@@ -17447,21 +17531,21 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    3 - Due in 31+ days: 43</t>
+          <t xml:space="preserve">    3 - Due in 31+ days: 44</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    4 - Past deadline: 66</t>
+          <t xml:space="preserve">    4 - Past deadline: 67</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    5 - No limit on file: 18</t>
+          <t xml:space="preserve">    5 - No limit on file: 16</t>
         </is>
       </c>
     </row>

--- a/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
+++ b/Specialty Claims 2026-S1/2026-03 March - Specialty Claims.xlsx
@@ -27,10 +27,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="MM/DD/YYYY"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="166" formatCode="MM/DD/YYYY"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -127,7 +126,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -282,12 +281,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -332,12 +331,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -382,12 +381,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -432,12 +431,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -482,12 +481,12 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Date the claim was processed, shown DD/MM/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date the claim was processed, shown MM/DD/YYYY. Pre-filled where a Note recorded one; blank otherwise for you to fill in.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Date you worked this claim, shown DD/MM/YYYY. Blank for you to fill in. Type it the way your Excel expects dates - the cell displays DD/MM/YYYY however it was entered.</t>
+        <t>Date you worked this claim, shown MM/DD/YYYY. Blank for you to fill in.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -17467,7 +17466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -17607,7 +17606,7 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "25/06/2026";  Date Worked 1: "12/08/2026".</t>
+          <t>Example of the expected format - Claim Status: "Denied";  Notes: "Corrected service line 1 - resubmitted";  Processed Date: "06/25/2026";  Date Worked 1: "08/12/2026".</t>
         </is>
       </c>
     </row>
@@ -17624,46 +17623,39 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Both are real dates displayed DD/MM/YYYY. Processed Date is already filled in on the 13 claim lines whose Notes recorded one - the Note still carries the original wording, so nothing was lost. Date Worked 1 starts empty.</t>
+          <t>Both are real dates displayed MM/DD/YYYY, the same order as every other date column in these files and as the source data. Processed Date is already filled in on the 13 claim lines whose Notes recorded one - the Note still carries the original wording, so nothing was lost. Date Worked 1 starts empty.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Careful when typing into them: Excel reads what you type using its own date setting, not the DD/MM/YYYY the cell displays. On a US Excel, typing 06/25/2026 gives 25 June and the cell then shows 25/06/2026. Type the date the way your Excel expects it and let the cell do the formatting, or check the formula bar afterwards. Every other date column in these files is MM/DD/YYYY, as in the source data.</t>
-        </is>
-      </c>
+      <c r="A26" s="11" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr"/>
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>How this file feeds the master</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>How this file feeds the master</t>
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 1,086 claim lines for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>'ALL Claims 2026-S1 - Master.xlsx' (same folder) holds all 1,086 claim lines for 2026 S1. Its Claim Status and Notes columns are formulas that read this file, so anything you type in columns A and B here shows up there. Keep both files in the same folder, keep the file name unchanged, and save this file before opening the master.</t>
+          <t>The link is matched on Line ID (last column), not on row position, so sorting and filtering these sheets is safe. Do not edit or delete the Line ID column, and do not rename the specialty sheet tabs.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>The link is matched on Line ID (last column), not on row position, so sorting and filtering these sheets is safe. Do not edit or delete the Line ID column, and do not rename the specialty sheet tabs.</t>
-        </is>
-      </c>
+      <c r="A30" s="11" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Everything else in this file is a static copy of the source data from 'Specialty Claims Pending 2026-S1.xlsx' (sheet 'Merged').</t>
         </is>
